--- a/backup/mantra-records.xlsx
+++ b/backup/mantra-records.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="60">
   <si>
     <t>时间戳</t>
   </si>
@@ -118,6 +118,51 @@
   </si>
   <si>
     <t>mrlz63f3-hptnt4</t>
+  </si>
+  <si>
+    <t>mrmnxcae-ptljyv</t>
+  </si>
+  <si>
+    <t>mrmnxkul-9vxo1d</t>
+  </si>
+  <si>
+    <t>mrmnxmpg-aqu6il</t>
+  </si>
+  <si>
+    <t>mrmnxphe-pc5phs</t>
+  </si>
+  <si>
+    <t>mrmnxwwh-qrg6fn</t>
+  </si>
+  <si>
+    <t>mrmny0y6-r2am2y</t>
+  </si>
+  <si>
+    <t>mrmny3yq-ubjiwg</t>
+  </si>
+  <si>
+    <t>mrmny6mi-re8jse</t>
+  </si>
+  <si>
+    <t>mrmnyk1x-1zs035</t>
+  </si>
+  <si>
+    <t>mrmonl7s-f3340b</t>
+  </si>
+  <si>
+    <t>mrmot70n-kson18</t>
+  </si>
+  <si>
+    <t>mrmwzite-qcg8km</t>
+  </si>
+  <si>
+    <t>mrmysspi-bwszzv</t>
+  </si>
+  <si>
+    <t>mrmyu3xp-dcjblp</t>
+  </si>
+  <si>
+    <t>mrmzbuii-wqptl2</t>
   </si>
   <si>
     <t>历史基数</t>
@@ -717,6 +762,261 @@
         <v>34</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2">
+        <v>46219.36083100694</v>
+      </c>
+      <c r="B17" s="3">
+        <v>46219.0</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="4">
+        <v>2200.0</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2">
+        <v>46219.36095940972</v>
+      </c>
+      <c r="B18" s="3">
+        <v>46219.0</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="4">
+        <v>220.0</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2">
+        <v>46219.36098726852</v>
+      </c>
+      <c r="B19" s="3">
+        <v>46219.0</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2">
+        <v>46219.36102891204</v>
+      </c>
+      <c r="B20" s="3">
+        <v>46219.0</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2">
+        <v>46219.361140196765</v>
+      </c>
+      <c r="B21" s="3">
+        <v>46219.0</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2">
+        <v>46219.36120090278</v>
+      </c>
+      <c r="B22" s="3">
+        <v>46219.0</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="4">
+        <v>1100.0</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2">
+        <v>46219.361246134256</v>
+      </c>
+      <c r="B23" s="3">
+        <v>46219.0</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2">
+        <v>46219.36128604166</v>
+      </c>
+      <c r="B24" s="3">
+        <v>46219.0</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2">
+        <v>46219.36148746528</v>
+      </c>
+      <c r="B25" s="3">
+        <v>46219.0</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="4">
+        <v>90.0</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2">
+        <v>46219.37500490741</v>
+      </c>
+      <c r="B26" s="3">
+        <v>46219.0</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="4">
+        <v>500.0</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2">
+        <v>46219.378031932865</v>
+      </c>
+      <c r="B27" s="3">
+        <v>46219.0</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2">
+        <v>46219.53696891204</v>
+      </c>
+      <c r="B28" s="3">
+        <v>46219.0</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2">
+        <v>46219.57221748843</v>
+      </c>
+      <c r="B29" s="3">
+        <v>46219.0</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="4">
+        <v>300.0</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2">
+        <v>46219.572925706016</v>
+      </c>
+      <c r="B30" s="3">
+        <v>46219.0</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30" s="4">
+        <v>21.0</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2">
+        <v>46219.582504375</v>
+      </c>
+      <c r="B31" s="3">
+        <v>46219.0</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D31" s="4">
+        <v>100.0</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -734,10 +1034,10 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2">
@@ -748,7 +1048,7 @@
         <v>2382681.0</v>
       </c>
       <c r="C2" s="4">
-        <v>2200.0</v>
+        <v>4400.0</v>
       </c>
     </row>
     <row r="3">
@@ -759,7 +1059,7 @@
         <v>2778093.0</v>
       </c>
       <c r="C3" s="4">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
     </row>
     <row r="4">
@@ -770,7 +1070,7 @@
         <v>158521.0</v>
       </c>
       <c r="C4" s="4">
-        <v>330.0</v>
+        <v>630.0</v>
       </c>
     </row>
     <row r="5">
@@ -781,7 +1081,7 @@
         <v>169321.0</v>
       </c>
       <c r="C5" s="4">
-        <v>220.0</v>
+        <v>440.0</v>
       </c>
     </row>
     <row r="6">
@@ -792,7 +1092,7 @@
         <v>5820554.0</v>
       </c>
       <c r="C6" s="4">
-        <v>110.0</v>
+        <v>220.0</v>
       </c>
     </row>
     <row r="7">
@@ -803,7 +1103,7 @@
         <v>1425700.0</v>
       </c>
       <c r="C7" s="4">
-        <v>110.0</v>
+        <v>220.0</v>
       </c>
     </row>
     <row r="8">
@@ -814,7 +1114,7 @@
         <v>890948.0</v>
       </c>
       <c r="C8" s="4">
-        <v>110.0</v>
+        <v>220.0</v>
       </c>
     </row>
     <row r="9">
@@ -825,7 +1125,7 @@
         <v>552569.0</v>
       </c>
       <c r="C9" s="4">
-        <v>110.0</v>
+        <v>220.0</v>
       </c>
     </row>
     <row r="10">
@@ -836,7 +1136,7 @@
         <v>139781.0</v>
       </c>
       <c r="C10" s="4">
-        <v>90.0</v>
+        <v>180.0</v>
       </c>
     </row>
     <row r="11">
@@ -847,7 +1147,7 @@
         <v>9031.0</v>
       </c>
       <c r="C11" s="4">
-        <v>21.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="12">
@@ -858,7 +1158,7 @@
         <v>1123250.0</v>
       </c>
       <c r="C12" s="4">
-        <v>1100.0</v>
+        <v>2200.0</v>
       </c>
     </row>
     <row r="13">
@@ -869,7 +1169,7 @@
         <v>1832.0</v>
       </c>
       <c r="C13" s="4">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="14">
@@ -880,7 +1180,7 @@
         <v>8100.0</v>
       </c>
       <c r="C14" s="4">
-        <v>50.0</v>
+        <v>150.0</v>
       </c>
     </row>
     <row r="15">
@@ -891,7 +1191,7 @@
         <v>639.0</v>
       </c>
       <c r="C15" s="4">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="16">
@@ -902,7 +1202,7 @@
         <v>219463.0</v>
       </c>
       <c r="C16" s="4">
-        <v>110.0</v>
+        <v>220.0</v>
       </c>
     </row>
   </sheetData>
@@ -924,19 +1224,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2">
@@ -953,7 +1253,7 @@
         <v>1000.0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
@@ -970,7 +1270,7 @@
         <v>100.0</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4">
@@ -987,7 +1287,7 @@
         <v>100.0</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5">
@@ -1004,7 +1304,7 @@
         <v>10.0</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
@@ -1021,7 +1321,7 @@
         <v>10.0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
@@ -1038,7 +1338,7 @@
         <v>100.0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8">
@@ -1055,7 +1355,7 @@
         <v>10.0</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9">
@@ -1072,7 +1372,7 @@
         <v>100.0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
@@ -1123,7 +1423,7 @@
         <v>100.0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13">
@@ -1140,7 +1440,7 @@
         <v>1.0</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14">
@@ -1157,7 +1457,7 @@
         <v>10.0</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
@@ -1174,7 +1474,7 @@
         <v>7.0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16">
@@ -1191,7 +1491,7 @@
         <v>1.0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/backup/mantra-records.xlsx
+++ b/backup/mantra-records.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="81">
   <si>
     <t>时间戳</t>
   </si>
@@ -165,6 +165,66 @@
     <t>mrmzbuii-wqptl2</t>
   </si>
   <si>
+    <t>金刚桥外皈依</t>
+  </si>
+  <si>
+    <t>mro5099x-4w4wei</t>
+  </si>
+  <si>
+    <t>mro50djk-ni0c05</t>
+  </si>
+  <si>
+    <t>mro50n10-6n7mca</t>
+  </si>
+  <si>
+    <t>mro50pr5-ba4q1f</t>
+  </si>
+  <si>
+    <t>mro50s05-8hldb4</t>
+  </si>
+  <si>
+    <t>mro50tqi-ym2tm4</t>
+  </si>
+  <si>
+    <t>mro50vp4-l9mvh6</t>
+  </si>
+  <si>
+    <t>mro511px-fp5lh8</t>
+  </si>
+  <si>
+    <t>mro515a9-7pvqjh</t>
+  </si>
+  <si>
+    <t>mro519gn-wi271r</t>
+  </si>
+  <si>
+    <t>mro51df8-h1ixy1</t>
+  </si>
+  <si>
+    <t>mroc5o4k-bcwp82</t>
+  </si>
+  <si>
+    <t>mrocjel3-q1iz1e</t>
+  </si>
+  <si>
+    <t>mrodtrjr-0kjy8c</t>
+  </si>
+  <si>
+    <t>mrodxpgp-shvpcu</t>
+  </si>
+  <si>
+    <t>mrofszf8-0l9qc9</t>
+  </si>
+  <si>
+    <t>mroglyuy-blvtx3</t>
+  </si>
+  <si>
+    <t>mrooxl6c-beb9by</t>
+  </si>
+  <si>
+    <t>mroyev20-puwvy0</t>
+  </si>
+  <si>
     <t>历史基数</t>
   </si>
   <si>
@@ -184,6 +244,9 @@
   </si>
   <si>
     <t>组别</t>
+  </si>
+  <si>
+    <t>金刚桥</t>
   </si>
   <si>
     <t>心咒</t>
@@ -1017,6 +1080,329 @@
         <v>49</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2">
+        <v>46220.39272579861</v>
+      </c>
+      <c r="B32" s="3">
+        <v>46220.0</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D32" s="4">
+        <v>330.0</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2">
+        <v>46220.39278981481</v>
+      </c>
+      <c r="B33" s="3">
+        <v>46220.0</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" s="4">
+        <v>330.0</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2">
+        <v>46220.392932083334</v>
+      </c>
+      <c r="B34" s="3">
+        <v>46220.0</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34" s="4">
+        <v>1100.0</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2">
+        <v>46220.392972974536</v>
+      </c>
+      <c r="B35" s="3">
+        <v>46220.0</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2">
+        <v>46220.39300672454</v>
+      </c>
+      <c r="B36" s="3">
+        <v>46220.0</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2">
+        <v>46220.393032708336</v>
+      </c>
+      <c r="B37" s="3">
+        <v>46220.0</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2">
+        <v>46220.39306212963</v>
+      </c>
+      <c r="B38" s="3">
+        <v>46220.0</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D38" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2">
+        <v>46220.39315246527</v>
+      </c>
+      <c r="B39" s="3">
+        <v>46220.0</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" s="4">
+        <v>500.0</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2">
+        <v>46220.3932059375</v>
+      </c>
+      <c r="B40" s="3">
+        <v>46220.0</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2">
+        <v>46220.39326859954</v>
+      </c>
+      <c r="B41" s="3">
+        <v>46220.0</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="4">
+        <v>90.0</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2">
+        <v>46220.39332800926</v>
+      </c>
+      <c r="B42" s="3">
+        <v>46220.0</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D42" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2">
+        <v>46220.53172856482</v>
+      </c>
+      <c r="B43" s="3">
+        <v>46220.0</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D43" s="4">
+        <v>500.0</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2">
+        <v>46220.53914545139</v>
+      </c>
+      <c r="B44" s="3">
+        <v>46220.0</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D44" s="4">
+        <v>350.0</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2">
+        <v>46220.56417989584</v>
+      </c>
+      <c r="B45" s="3">
+        <v>46220.0</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="4">
+        <v>300.0</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2">
+        <v>46220.566308622685</v>
+      </c>
+      <c r="B46" s="3">
+        <v>46220.0</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D46" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2">
+        <v>46220.60263800926</v>
+      </c>
+      <c r="B47" s="3">
+        <v>46220.0</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D47" s="4">
+        <v>100.0</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2">
+        <v>46220.61828956018</v>
+      </c>
+      <c r="B48" s="3">
+        <v>46220.0</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D48" s="4">
+        <v>21.0</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2">
+        <v>46220.78008434028</v>
+      </c>
+      <c r="B49" s="3">
+        <v>46220.0</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D49" s="4">
+        <v>100.0</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2">
+        <v>46220.9643725</v>
+      </c>
+      <c r="B50" s="3">
+        <v>46220.0</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D50" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -1028,16 +1414,20 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="21.38"/>
+    <col customWidth="1" min="2" max="2" width="18.63"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2">
@@ -1048,7 +1438,7 @@
         <v>2382681.0</v>
       </c>
       <c r="C2" s="4">
-        <v>4400.0</v>
+        <v>5580.0</v>
       </c>
     </row>
     <row r="3">
@@ -1059,7 +1449,7 @@
         <v>2778093.0</v>
       </c>
       <c r="C3" s="4">
-        <v>1000.0</v>
+        <v>1500.0</v>
       </c>
     </row>
     <row r="4">
@@ -1070,7 +1460,7 @@
         <v>158521.0</v>
       </c>
       <c r="C4" s="4">
-        <v>630.0</v>
+        <v>930.0</v>
       </c>
     </row>
     <row r="5">
@@ -1081,7 +1471,7 @@
         <v>169321.0</v>
       </c>
       <c r="C5" s="4">
-        <v>440.0</v>
+        <v>550.0</v>
       </c>
     </row>
     <row r="6">
@@ -1092,7 +1482,7 @@
         <v>5820554.0</v>
       </c>
       <c r="C6" s="4">
-        <v>220.0</v>
+        <v>330.0</v>
       </c>
     </row>
     <row r="7">
@@ -1103,7 +1493,7 @@
         <v>1425700.0</v>
       </c>
       <c r="C7" s="4">
-        <v>220.0</v>
+        <v>330.0</v>
       </c>
     </row>
     <row r="8">
@@ -1114,7 +1504,7 @@
         <v>890948.0</v>
       </c>
       <c r="C8" s="4">
-        <v>220.0</v>
+        <v>330.0</v>
       </c>
     </row>
     <row r="9">
@@ -1125,7 +1515,7 @@
         <v>552569.0</v>
       </c>
       <c r="C9" s="4">
-        <v>220.0</v>
+        <v>330.0</v>
       </c>
     </row>
     <row r="10">
@@ -1136,7 +1526,7 @@
         <v>139781.0</v>
       </c>
       <c r="C10" s="4">
-        <v>180.0</v>
+        <v>270.0</v>
       </c>
     </row>
     <row r="11">
@@ -1147,7 +1537,7 @@
         <v>9031.0</v>
       </c>
       <c r="C11" s="4">
-        <v>42.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="12">
@@ -1158,7 +1548,7 @@
         <v>1123250.0</v>
       </c>
       <c r="C12" s="4">
-        <v>2200.0</v>
+        <v>3300.0</v>
       </c>
     </row>
     <row r="13">
@@ -1169,7 +1559,7 @@
         <v>1832.0</v>
       </c>
       <c r="C13" s="4">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="14">
@@ -1180,7 +1570,7 @@
         <v>8100.0</v>
       </c>
       <c r="C14" s="4">
-        <v>150.0</v>
+        <v>250.0</v>
       </c>
     </row>
     <row r="15">
@@ -1191,7 +1581,7 @@
         <v>639.0</v>
       </c>
       <c r="C15" s="4">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="16">
@@ -1202,7 +1592,18 @@
         <v>219463.0</v>
       </c>
       <c r="C16" s="4">
-        <v>220.0</v>
+        <v>330.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="C17" s="4">
+        <v>430.0</v>
       </c>
     </row>
   </sheetData>
@@ -1217,6 +1618,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
+    <col customWidth="1" min="1" max="1" width="18.88"/>
     <col customWidth="1" min="2" max="2" width="11.63"/>
     <col customWidth="1" min="3" max="3" width="10.75"/>
     <col customWidth="1" min="4" max="4" width="10.5"/>
@@ -1224,121 +1626,121 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="4">
-        <v>3000.0</v>
+        <v>50</v>
+      </c>
+      <c r="B2" s="1">
+        <v>330.0</v>
       </c>
       <c r="C2" s="1">
-        <v>2000.0</v>
+        <v>110.0</v>
       </c>
       <c r="D2" s="1">
-        <v>1000.0</v>
+        <v>100.0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B3" s="4">
-        <v>550.0</v>
+        <v>3000.0</v>
       </c>
       <c r="C3" s="1">
-        <v>500.0</v>
-      </c>
-      <c r="D3" s="4">
-        <v>100.0</v>
+        <v>2000.0</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1000.0</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="4">
-        <v>330.0</v>
+        <v>27</v>
+      </c>
+      <c r="B4" s="1">
+        <v>110.0</v>
       </c>
       <c r="C4" s="1">
-        <v>200.0</v>
-      </c>
-      <c r="D4" s="4">
         <v>100.0</v>
       </c>
+      <c r="D4" s="1">
+        <v>1.0</v>
+      </c>
       <c r="E4" s="1" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B5" s="4">
-        <v>220.0</v>
+        <v>1100.0</v>
       </c>
       <c r="C5" s="4">
         <v>110.0</v>
       </c>
       <c r="D5" s="4">
-        <v>10.0</v>
+        <v>100.0</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B6" s="4">
-        <v>110.0</v>
+        <v>220.0</v>
       </c>
       <c r="C6" s="4">
-        <v>100.0</v>
+        <v>110.0</v>
       </c>
       <c r="D6" s="4">
         <v>10.0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1">
-        <v>550.0</v>
-      </c>
-      <c r="C7" s="1">
-        <v>110.0</v>
+        <v>13</v>
+      </c>
+      <c r="B7" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="C7" s="4">
+        <v>100.0</v>
       </c>
       <c r="D7" s="4">
-        <v>100.0</v>
+        <v>10.0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -1355,7 +1757,7 @@
         <v>10.0</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9">
@@ -1372,126 +1774,143 @@
         <v>100.0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B10" s="4">
-        <v>110.0</v>
-      </c>
-      <c r="C10" s="4">
+        <v>550.0</v>
+      </c>
+      <c r="C10" s="1">
+        <v>500.0</v>
+      </c>
+      <c r="D10" s="4">
         <v>100.0</v>
       </c>
-      <c r="D10" s="1">
-        <v>90.0</v>
-      </c>
       <c r="E10" s="1" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="4">
-        <v>21.0</v>
-      </c>
-      <c r="C11" s="4">
-        <v>7.0</v>
+        <v>15</v>
+      </c>
+      <c r="B11" s="1">
+        <v>550.0</v>
+      </c>
+      <c r="C11" s="1">
+        <v>110.0</v>
       </c>
       <c r="D11" s="4">
-        <v>1.0</v>
+        <v>100.0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="B12" s="4">
-        <v>1100.0</v>
-      </c>
-      <c r="C12" s="4">
-        <v>110.0</v>
+        <v>330.0</v>
+      </c>
+      <c r="C12" s="1">
+        <v>300.0</v>
       </c>
       <c r="D12" s="4">
         <v>100.0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="1">
-        <v>5.0</v>
+        <v>19</v>
+      </c>
+      <c r="B13" s="4">
+        <v>110.0</v>
       </c>
       <c r="C13" s="4">
-        <v>3.0</v>
+        <v>100.0</v>
       </c>
       <c r="D13" s="1">
-        <v>1.0</v>
+        <v>90.0</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B14" s="4">
-        <v>100.0</v>
+        <v>21.0</v>
       </c>
       <c r="C14" s="4">
-        <v>50.0</v>
+        <v>7.0</v>
       </c>
       <c r="D14" s="4">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="4">
-        <v>1.0</v>
+        <v>33</v>
+      </c>
+      <c r="B15" s="1">
+        <v>5.0</v>
       </c>
       <c r="C15" s="4">
         <v>3.0</v>
       </c>
-      <c r="D15" s="4">
-        <v>7.0</v>
+      <c r="D15" s="1">
+        <v>1.0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="1">
-        <v>110.0</v>
-      </c>
-      <c r="C16" s="1">
+        <v>29</v>
+      </c>
+      <c r="B16" s="4">
         <v>100.0</v>
       </c>
-      <c r="D16" s="1">
+      <c r="C16" s="4">
+        <v>50.0</v>
+      </c>
+      <c r="D16" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="4">
         <v>1.0</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>57</v>
+      <c r="C17" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D17" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/backup/mantra-records.xlsx
+++ b/backup/mantra-records.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="97">
   <si>
     <t>时间戳</t>
   </si>
@@ -223,6 +223,54 @@
   </si>
   <si>
     <t>mroyev20-puwvy0</t>
+  </si>
+  <si>
+    <t>mrpp05gp-02fnvx</t>
+  </si>
+  <si>
+    <t>mrpp0dgu-lo7di3</t>
+  </si>
+  <si>
+    <t>mrprbu8k-n7z5xp</t>
+  </si>
+  <si>
+    <t>mrprdolz-xs3lva</t>
+  </si>
+  <si>
+    <t>mrprds7j-hs5ai7</t>
+  </si>
+  <si>
+    <t>mrprdub4-8wviny</t>
+  </si>
+  <si>
+    <t>mrpre5xh-bvuz1p</t>
+  </si>
+  <si>
+    <t>mrprecw3-99bxxp</t>
+  </si>
+  <si>
+    <t>mrpt5qma-l1bcx5</t>
+  </si>
+  <si>
+    <t>mrpt5u63-dcod8r</t>
+  </si>
+  <si>
+    <t>mrpt634o-vnmuc2</t>
+  </si>
+  <si>
+    <t>mrpunbiw-4n8ol3</t>
+  </si>
+  <si>
+    <t>mrpunhcy-qt0wxj</t>
+  </si>
+  <si>
+    <t>mrpunqm3-zmngi0</t>
+  </si>
+  <si>
+    <t>mrpunzza-lhyzmm</t>
+  </si>
+  <si>
+    <t>mrpuv8hq-5mqwtg</t>
   </si>
   <si>
     <t>历史基数</t>
@@ -1403,6 +1451,278 @@
         <v>69</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="2">
+        <v>46221.481308622686</v>
+      </c>
+      <c r="B51" s="3">
+        <v>46221.0</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D51" s="4">
+        <v>350.0</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2">
+        <v>46221.481428680556</v>
+      </c>
+      <c r="B52" s="3">
+        <v>46221.0</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D52" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2">
+        <v>46221.52650024305</v>
+      </c>
+      <c r="B53" s="3">
+        <v>46221.0</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D53" s="4">
+        <v>2200.0</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2">
+        <v>46221.52749582176</v>
+      </c>
+      <c r="B54" s="3">
+        <v>46221.0</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D54" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2">
+        <v>46221.52754980324</v>
+      </c>
+      <c r="B55" s="3">
+        <v>46221.0</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2">
+        <v>46221.527581296294</v>
+      </c>
+      <c r="B56" s="3">
+        <v>46221.0</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D56" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2">
+        <v>46221.527755613424</v>
+      </c>
+      <c r="B57" s="3">
+        <v>46221.0</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D57" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2">
+        <v>46221.52786003472</v>
+      </c>
+      <c r="B58" s="3">
+        <v>46221.0</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D58" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2">
+        <v>46221.56208596065</v>
+      </c>
+      <c r="B59" s="3">
+        <v>46221.0</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D59" s="4">
+        <v>1100.0</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2">
+        <v>46221.562139201385</v>
+      </c>
+      <c r="B60" s="3">
+        <v>46221.0</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D60" s="4">
+        <v>220.0</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2">
+        <v>46221.56227361111</v>
+      </c>
+      <c r="B61" s="3">
+        <v>46221.0</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D61" s="4">
+        <v>1100.0</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2">
+        <v>46221.59101953704</v>
+      </c>
+      <c r="B62" s="3">
+        <v>46221.0</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D62" s="4">
+        <v>880.0</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2">
+        <v>46221.59110706019</v>
+      </c>
+      <c r="B63" s="3">
+        <v>46221.0</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D63" s="4">
+        <v>100.0</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2">
+        <v>46221.591245868054</v>
+      </c>
+      <c r="B64" s="3">
+        <v>46221.0</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D64" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2">
+        <v>46221.59138636574</v>
+      </c>
+      <c r="B65" s="3">
+        <v>46221.0</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D65" s="4">
+        <v>330.0</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2">
+        <v>46221.5952940625</v>
+      </c>
+      <c r="B66" s="3">
+        <v>46221.0</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D66" s="4">
+        <v>21.0</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -1424,10 +1744,10 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2">
@@ -1438,7 +1758,7 @@
         <v>2382681.0</v>
       </c>
       <c r="C2" s="4">
-        <v>5580.0</v>
+        <v>7780.0</v>
       </c>
     </row>
     <row r="3">
@@ -1449,7 +1769,7 @@
         <v>2778093.0</v>
       </c>
       <c r="C3" s="4">
-        <v>1500.0</v>
+        <v>2600.0</v>
       </c>
     </row>
     <row r="4">
@@ -1460,7 +1780,7 @@
         <v>158521.0</v>
       </c>
       <c r="C4" s="4">
-        <v>930.0</v>
+        <v>1260.0</v>
       </c>
     </row>
     <row r="5">
@@ -1471,7 +1791,7 @@
         <v>169321.0</v>
       </c>
       <c r="C5" s="4">
-        <v>550.0</v>
+        <v>770.0</v>
       </c>
     </row>
     <row r="6">
@@ -1482,7 +1802,7 @@
         <v>5820554.0</v>
       </c>
       <c r="C6" s="4">
-        <v>330.0</v>
+        <v>440.0</v>
       </c>
     </row>
     <row r="7">
@@ -1493,7 +1813,7 @@
         <v>1425700.0</v>
       </c>
       <c r="C7" s="4">
-        <v>330.0</v>
+        <v>1210.0</v>
       </c>
     </row>
     <row r="8">
@@ -1504,7 +1824,7 @@
         <v>890948.0</v>
       </c>
       <c r="C8" s="4">
-        <v>330.0</v>
+        <v>440.0</v>
       </c>
     </row>
     <row r="9">
@@ -1515,7 +1835,7 @@
         <v>552569.0</v>
       </c>
       <c r="C9" s="4">
-        <v>330.0</v>
+        <v>440.0</v>
       </c>
     </row>
     <row r="10">
@@ -1526,7 +1846,7 @@
         <v>139781.0</v>
       </c>
       <c r="C10" s="4">
-        <v>270.0</v>
+        <v>380.0</v>
       </c>
     </row>
     <row r="11">
@@ -1537,7 +1857,7 @@
         <v>9031.0</v>
       </c>
       <c r="C11" s="4">
-        <v>63.0</v>
+        <v>84.0</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1868,7 @@
         <v>1123250.0</v>
       </c>
       <c r="C12" s="4">
-        <v>3300.0</v>
+        <v>4400.0</v>
       </c>
     </row>
     <row r="13">
@@ -1559,7 +1879,7 @@
         <v>1832.0</v>
       </c>
       <c r="C13" s="4">
-        <v>7.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="14">
@@ -1570,7 +1890,7 @@
         <v>8100.0</v>
       </c>
       <c r="C14" s="4">
-        <v>250.0</v>
+        <v>350.0</v>
       </c>
     </row>
     <row r="15">
@@ -1581,7 +1901,7 @@
         <v>639.0</v>
       </c>
       <c r="C15" s="4">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="16">
@@ -1592,7 +1912,7 @@
         <v>219463.0</v>
       </c>
       <c r="C16" s="4">
-        <v>330.0</v>
+        <v>440.0</v>
       </c>
     </row>
     <row r="17">
@@ -1603,7 +1923,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" s="4">
-        <v>430.0</v>
+        <v>780.0</v>
       </c>
     </row>
   </sheetData>
@@ -1626,19 +1946,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2">
@@ -1655,7 +1975,7 @@
         <v>100.0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3">
@@ -1672,7 +1992,7 @@
         <v>1000.0</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4">
@@ -1689,7 +2009,7 @@
         <v>1.0</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5">
@@ -1706,7 +2026,7 @@
         <v>100.0</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6">
@@ -1723,7 +2043,7 @@
         <v>10.0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7">
@@ -1740,7 +2060,7 @@
         <v>10.0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8">
@@ -1757,7 +2077,7 @@
         <v>10.0</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9">
@@ -1774,7 +2094,7 @@
         <v>100.0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10">
@@ -1791,7 +2111,7 @@
         <v>100.0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11">
@@ -1808,7 +2128,7 @@
         <v>100.0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12">
@@ -1825,7 +2145,7 @@
         <v>100.0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -1876,7 +2196,7 @@
         <v>1.0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16">
@@ -1893,7 +2213,7 @@
         <v>10.0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17">
@@ -1910,7 +2230,7 @@
         <v>7.0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/backup/mantra-records.xlsx
+++ b/backup/mantra-records.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="114">
   <si>
     <t>时间戳</t>
   </si>
@@ -271,6 +271,57 @@
   </si>
   <si>
     <t>mrpuv8hq-5mqwtg</t>
+  </si>
+  <si>
+    <t>mrr89msf-xxepa5</t>
+  </si>
+  <si>
+    <t>mrr89t9l-6g28ng</t>
+  </si>
+  <si>
+    <t>mrr89wnf-tdkhz6</t>
+  </si>
+  <si>
+    <t>mrr89ygw-1yx362</t>
+  </si>
+  <si>
+    <t>mrr8a1g8-ri7k6j</t>
+  </si>
+  <si>
+    <t>mrr8a6yl-5qu0lz</t>
+  </si>
+  <si>
+    <t>mrr8uacv-bi1ik2</t>
+  </si>
+  <si>
+    <t>mrr8ud0k-a7a5vd</t>
+  </si>
+  <si>
+    <t>mrr8ug4s-q3mghh</t>
+  </si>
+  <si>
+    <t>mrr8ul4v-wi06ji</t>
+  </si>
+  <si>
+    <t>mrr8unt2-ctknz1</t>
+  </si>
+  <si>
+    <t>mrr8urie-9e5ek0</t>
+  </si>
+  <si>
+    <t>mrre092w-9ijpo4</t>
+  </si>
+  <si>
+    <t>mrregxwd-a5jhra</t>
+  </si>
+  <si>
+    <t>mrrpkycg-0ntkvj</t>
+  </si>
+  <si>
+    <t>mrrqes2k-b495rl</t>
+  </si>
+  <si>
+    <t>mrrqwh6y-dp20zq</t>
   </si>
   <si>
     <t>历史基数</t>
@@ -1723,6 +1774,295 @@
         <v>85</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="2">
+        <v>46222.55562850695</v>
+      </c>
+      <c r="B67" s="3">
+        <v>46222.0</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D67" s="4">
+        <v>300.0</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2">
+        <v>46222.555725659724</v>
+      </c>
+      <c r="B68" s="3">
+        <v>46222.0</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D68" s="4">
+        <v>1100.0</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2">
+        <v>46222.555776423615</v>
+      </c>
+      <c r="B69" s="3">
+        <v>46222.0</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D69" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2">
+        <v>46222.55580371528</v>
+      </c>
+      <c r="B70" s="3">
+        <v>46222.0</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D70" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2">
+        <v>46222.55584842592</v>
+      </c>
+      <c r="B71" s="3">
+        <v>46222.0</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D71" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2">
+        <v>46222.55593107639</v>
+      </c>
+      <c r="B72" s="3">
+        <v>46222.0</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D72" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2">
+        <v>46222.566782037036</v>
+      </c>
+      <c r="B73" s="3">
+        <v>46222.0</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D73" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2">
+        <v>46222.566821898145</v>
+      </c>
+      <c r="B74" s="3">
+        <v>46222.0</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D74" s="4">
+        <v>1100.0</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2">
+        <v>46222.566868657406</v>
+      </c>
+      <c r="B75" s="3">
+        <v>46222.0</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D75" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2">
+        <v>46222.56694369213</v>
+      </c>
+      <c r="B76" s="3">
+        <v>46222.0</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D76" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2">
+        <v>46222.56698377315</v>
+      </c>
+      <c r="B77" s="3">
+        <v>46222.0</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D77" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2">
+        <v>46222.5670393287</v>
+      </c>
+      <c r="B78" s="3">
+        <v>46222.0</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D78" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2">
+        <v>46222.667202881945</v>
+      </c>
+      <c r="B79" s="3">
+        <v>46222.0</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D79" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2">
+        <v>46222.676215150466</v>
+      </c>
+      <c r="B80" s="3">
+        <v>46222.0</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D80" s="4">
+        <v>21.0</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2">
+        <v>46222.89222185186</v>
+      </c>
+      <c r="B81" s="3">
+        <v>46222.0</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D81" s="4">
+        <v>220.0</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2">
+        <v>46222.90832773148</v>
+      </c>
+      <c r="B82" s="3">
+        <v>46222.0</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D82" s="4">
+        <v>108.0</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2">
+        <v>46222.917884560185</v>
+      </c>
+      <c r="B83" s="3">
+        <v>46222.0</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D83" s="4">
+        <v>100.0</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -1744,10 +2084,10 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2">
@@ -1758,7 +2098,7 @@
         <v>2382681.0</v>
       </c>
       <c r="C2" s="4">
-        <v>7780.0</v>
+        <v>8880.0</v>
       </c>
     </row>
     <row r="3">
@@ -1769,7 +2109,7 @@
         <v>2778093.0</v>
       </c>
       <c r="C3" s="4">
-        <v>2600.0</v>
+        <v>2710.0</v>
       </c>
     </row>
     <row r="4">
@@ -1780,7 +2120,7 @@
         <v>158521.0</v>
       </c>
       <c r="C4" s="4">
-        <v>1260.0</v>
+        <v>1370.0</v>
       </c>
     </row>
     <row r="5">
@@ -1791,7 +2131,7 @@
         <v>169321.0</v>
       </c>
       <c r="C5" s="4">
-        <v>770.0</v>
+        <v>880.0</v>
       </c>
     </row>
     <row r="6">
@@ -1802,7 +2142,7 @@
         <v>5820554.0</v>
       </c>
       <c r="C6" s="4">
-        <v>440.0</v>
+        <v>550.0</v>
       </c>
     </row>
     <row r="7">
@@ -1813,7 +2153,7 @@
         <v>1425700.0</v>
       </c>
       <c r="C7" s="4">
-        <v>1210.0</v>
+        <v>1320.0</v>
       </c>
     </row>
     <row r="8">
@@ -1824,7 +2164,7 @@
         <v>890948.0</v>
       </c>
       <c r="C8" s="4">
-        <v>440.0</v>
+        <v>550.0</v>
       </c>
     </row>
     <row r="9">
@@ -1835,7 +2175,7 @@
         <v>552569.0</v>
       </c>
       <c r="C9" s="4">
-        <v>440.0</v>
+        <v>550.0</v>
       </c>
     </row>
     <row r="10">
@@ -1846,7 +2186,7 @@
         <v>139781.0</v>
       </c>
       <c r="C10" s="4">
-        <v>380.0</v>
+        <v>488.0</v>
       </c>
     </row>
     <row r="11">
@@ -1857,7 +2197,7 @@
         <v>9031.0</v>
       </c>
       <c r="C11" s="4">
-        <v>84.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="12">
@@ -1868,7 +2208,7 @@
         <v>1123250.0</v>
       </c>
       <c r="C12" s="4">
-        <v>4400.0</v>
+        <v>5500.0</v>
       </c>
     </row>
     <row r="13">
@@ -1879,7 +2219,7 @@
         <v>1832.0</v>
       </c>
       <c r="C13" s="4">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="14">
@@ -1890,7 +2230,7 @@
         <v>8100.0</v>
       </c>
       <c r="C14" s="4">
-        <v>350.0</v>
+        <v>450.0</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +2241,7 @@
         <v>639.0</v>
       </c>
       <c r="C15" s="4">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +2252,7 @@
         <v>219463.0</v>
       </c>
       <c r="C16" s="4">
-        <v>440.0</v>
+        <v>550.0</v>
       </c>
     </row>
     <row r="17">
@@ -1923,7 +2263,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" s="4">
-        <v>780.0</v>
+        <v>1300.0</v>
       </c>
     </row>
   </sheetData>
@@ -1946,19 +2286,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2">
@@ -1975,7 +2315,7 @@
         <v>100.0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3">
@@ -1992,7 +2332,7 @@
         <v>1000.0</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4">
@@ -2009,7 +2349,7 @@
         <v>1.0</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5">
@@ -2026,7 +2366,7 @@
         <v>100.0</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6">
@@ -2043,7 +2383,7 @@
         <v>10.0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7">
@@ -2060,7 +2400,7 @@
         <v>10.0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8">
@@ -2077,7 +2417,7 @@
         <v>10.0</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9">
@@ -2094,7 +2434,7 @@
         <v>100.0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10">
@@ -2111,7 +2451,7 @@
         <v>100.0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11">
@@ -2128,7 +2468,7 @@
         <v>100.0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12">
@@ -2145,7 +2485,7 @@
         <v>100.0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13">
@@ -2196,7 +2536,7 @@
         <v>1.0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -2213,7 +2553,7 @@
         <v>10.0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17">
@@ -2230,7 +2570,7 @@
         <v>7.0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/backup/mantra-records.xlsx
+++ b/backup/mantra-records.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="131">
   <si>
     <t>时间戳</t>
   </si>
@@ -322,6 +322,57 @@
   </si>
   <si>
     <t>mrrqwh6y-dp20zq</t>
+  </si>
+  <si>
+    <t>mrsd7ex5-2rprlu</t>
+  </si>
+  <si>
+    <t>mrsfiwuh-10zuj0</t>
+  </si>
+  <si>
+    <t>mrsgl5su-lrh19d</t>
+  </si>
+  <si>
+    <t>mrsgl86w-ts089o</t>
+  </si>
+  <si>
+    <t>mrsglbn2-rwunzm</t>
+  </si>
+  <si>
+    <t>mrsgldmm-cc4n9n</t>
+  </si>
+  <si>
+    <t>mrsglfvd-eslue9</t>
+  </si>
+  <si>
+    <t>mrsgljvy-gky4s1</t>
+  </si>
+  <si>
+    <t>mrsh3lu6-tr9bru</t>
+  </si>
+  <si>
+    <t>mrsha4em-dq57jq</t>
+  </si>
+  <si>
+    <t>mrsr6zbs-bqtnit</t>
+  </si>
+  <si>
+    <t>mrsr796e-vmocp6</t>
+  </si>
+  <si>
+    <t>mrt4k5e8-kuivrb</t>
+  </si>
+  <si>
+    <t>mrt4k865-njx7zm</t>
+  </si>
+  <si>
+    <t>mrt4lfv2-fqh44r</t>
+  </si>
+  <si>
+    <t>mrt4lo5a-v52mjf</t>
+  </si>
+  <si>
+    <t>mrt6pgpd-r4by96</t>
   </si>
   <si>
     <t>历史基数</t>
@@ -2063,6 +2114,295 @@
         <v>102</v>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="2">
+        <v>46223.35147047453</v>
+      </c>
+      <c r="B84" s="3">
+        <v>46223.0</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D84" s="4">
+        <v>330.0</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2">
+        <v>46223.39655936343</v>
+      </c>
+      <c r="B85" s="3">
+        <v>46223.0</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D85" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2">
+        <v>46223.41721368056</v>
+      </c>
+      <c r="B86" s="3">
+        <v>46223.0</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D86" s="4">
+        <v>1100.0</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2">
+        <v>46223.41724953704</v>
+      </c>
+      <c r="B87" s="3">
+        <v>46223.0</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D87" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2">
+        <v>46223.41730127315</v>
+      </c>
+      <c r="B88" s="3">
+        <v>46223.0</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D88" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2">
+        <v>46223.41733108796</v>
+      </c>
+      <c r="B89" s="3">
+        <v>46223.0</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D89" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2">
+        <v>46223.417364733796</v>
+      </c>
+      <c r="B90" s="3">
+        <v>46223.0</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D90" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2">
+        <v>46223.417424976855</v>
+      </c>
+      <c r="B91" s="3">
+        <v>46223.0</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D91" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2">
+        <v>46223.427174247685</v>
+      </c>
+      <c r="B92" s="3">
+        <v>46223.0</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D92" s="4">
+        <v>1100.0</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2">
+        <v>46223.43069275463</v>
+      </c>
+      <c r="B93" s="3">
+        <v>46223.0</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D93" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2">
+        <v>46223.623396574076</v>
+      </c>
+      <c r="B94" s="3">
+        <v>46223.0</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D94" s="4">
+        <v>330.0</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2">
+        <v>46223.6235443287</v>
+      </c>
+      <c r="B95" s="3">
+        <v>46223.0</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D95" s="4">
+        <v>50.0</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2">
+        <v>46223.883227592596</v>
+      </c>
+      <c r="B96" s="3">
+        <v>46223.0</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D96" s="4">
+        <v>660.0</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2">
+        <v>46223.883269224534</v>
+      </c>
+      <c r="B97" s="3">
+        <v>46223.0</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D97" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2">
+        <v>46223.88392460648</v>
+      </c>
+      <c r="B98" s="3">
+        <v>46223.0</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D98" s="4">
+        <v>21.0</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2">
+        <v>46223.884048865744</v>
+      </c>
+      <c r="B99" s="3">
+        <v>46223.0</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D99" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2">
+        <v>46223.92497723379</v>
+      </c>
+      <c r="B100" s="3">
+        <v>46223.0</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D100" s="4">
+        <v>50.0</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -2084,10 +2424,10 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2">
@@ -2098,7 +2438,7 @@
         <v>2382681.0</v>
       </c>
       <c r="C2" s="4">
-        <v>8880.0</v>
+        <v>9980.0</v>
       </c>
     </row>
     <row r="3">
@@ -2109,7 +2449,7 @@
         <v>2778093.0</v>
       </c>
       <c r="C3" s="4">
-        <v>2710.0</v>
+        <v>3370.0</v>
       </c>
     </row>
     <row r="4">
@@ -2120,7 +2460,7 @@
         <v>158521.0</v>
       </c>
       <c r="C4" s="4">
-        <v>1370.0</v>
+        <v>1700.0</v>
       </c>
     </row>
     <row r="5">
@@ -2131,7 +2471,7 @@
         <v>169321.0</v>
       </c>
       <c r="C5" s="4">
-        <v>880.0</v>
+        <v>990.0</v>
       </c>
     </row>
     <row r="6">
@@ -2142,7 +2482,7 @@
         <v>5820554.0</v>
       </c>
       <c r="C6" s="4">
-        <v>550.0</v>
+        <v>660.0</v>
       </c>
     </row>
     <row r="7">
@@ -2153,7 +2493,7 @@
         <v>1425700.0</v>
       </c>
       <c r="C7" s="4">
-        <v>1320.0</v>
+        <v>1430.0</v>
       </c>
     </row>
     <row r="8">
@@ -2164,7 +2504,7 @@
         <v>890948.0</v>
       </c>
       <c r="C8" s="4">
-        <v>550.0</v>
+        <v>660.0</v>
       </c>
     </row>
     <row r="9">
@@ -2175,7 +2515,7 @@
         <v>552569.0</v>
       </c>
       <c r="C9" s="4">
-        <v>550.0</v>
+        <v>660.0</v>
       </c>
     </row>
     <row r="10">
@@ -2186,7 +2526,7 @@
         <v>139781.0</v>
       </c>
       <c r="C10" s="4">
-        <v>488.0</v>
+        <v>598.0</v>
       </c>
     </row>
     <row r="11">
@@ -2197,7 +2537,7 @@
         <v>9031.0</v>
       </c>
       <c r="C11" s="4">
-        <v>105.0</v>
+        <v>126.0</v>
       </c>
     </row>
     <row r="12">
@@ -2208,7 +2548,7 @@
         <v>1123250.0</v>
       </c>
       <c r="C12" s="4">
-        <v>5500.0</v>
+        <v>6600.0</v>
       </c>
     </row>
     <row r="13">
@@ -2219,7 +2559,7 @@
         <v>1832.0</v>
       </c>
       <c r="C13" s="4">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="14">
@@ -2230,7 +2570,7 @@
         <v>8100.0</v>
       </c>
       <c r="C14" s="4">
-        <v>450.0</v>
+        <v>550.0</v>
       </c>
     </row>
     <row r="15">
@@ -2241,7 +2581,7 @@
         <v>639.0</v>
       </c>
       <c r="C15" s="4">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="16">
@@ -2252,7 +2592,7 @@
         <v>219463.0</v>
       </c>
       <c r="C16" s="4">
-        <v>550.0</v>
+        <v>660.0</v>
       </c>
     </row>
     <row r="17">
@@ -2263,7 +2603,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" s="4">
-        <v>1300.0</v>
+        <v>1630.0</v>
       </c>
     </row>
   </sheetData>
@@ -2286,19 +2626,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2">
@@ -2315,7 +2655,7 @@
         <v>100.0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3">
@@ -2332,7 +2672,7 @@
         <v>1000.0</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4">
@@ -2349,7 +2689,7 @@
         <v>1.0</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5">
@@ -2366,7 +2706,7 @@
         <v>100.0</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6">
@@ -2383,7 +2723,7 @@
         <v>10.0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7">
@@ -2400,7 +2740,7 @@
         <v>10.0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8">
@@ -2417,7 +2757,7 @@
         <v>10.0</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9">
@@ -2434,7 +2774,7 @@
         <v>100.0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10">
@@ -2451,7 +2791,7 @@
         <v>100.0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11">
@@ -2468,7 +2808,7 @@
         <v>100.0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12">
@@ -2485,7 +2825,7 @@
         <v>100.0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13">
@@ -2536,7 +2876,7 @@
         <v>1.0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16">
@@ -2553,7 +2893,7 @@
         <v>10.0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17">
@@ -2570,7 +2910,7 @@
         <v>7.0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/backup/mantra-records.xlsx
+++ b/backup/mantra-records.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="149">
   <si>
     <t>时间戳</t>
   </si>
@@ -373,6 +373,60 @@
   </si>
   <si>
     <t>mrt6pgpd-r4by96</t>
+  </si>
+  <si>
+    <t>mrtsegx1-cx6i6l</t>
+  </si>
+  <si>
+    <t>mrtseor7-km7w4x</t>
+  </si>
+  <si>
+    <t>mrtshtsw-9diw3b</t>
+  </si>
+  <si>
+    <t>mrtshw2x-mtt00y</t>
+  </si>
+  <si>
+    <t>mrtshymw-iyv2r8</t>
+  </si>
+  <si>
+    <t>mrtsi0j6-253pkg</t>
+  </si>
+  <si>
+    <t>mrtsi21b-ifiezp</t>
+  </si>
+  <si>
+    <t>mrtsi425-5h92gn</t>
+  </si>
+  <si>
+    <t>mrtsi7bv-8i7qsv</t>
+  </si>
+  <si>
+    <t>mrtumkcl-mov3bh</t>
+  </si>
+  <si>
+    <t>mrtumm5n-z7qthm</t>
+  </si>
+  <si>
+    <t>mrtumr60-1319es</t>
+  </si>
+  <si>
+    <t>mru2zpsd-6rl8mc</t>
+  </si>
+  <si>
+    <t>mru2zsyf-6s74hq</t>
+  </si>
+  <si>
+    <t>mru33x8b-bh4ago</t>
+  </si>
+  <si>
+    <t>mrueaihk-hb7ltm</t>
+  </si>
+  <si>
+    <t>mruealnl-7y5kel</t>
+  </si>
+  <si>
+    <t>mruj2cq2-u3vmol</t>
   </si>
   <si>
     <t>历史基数</t>
@@ -2403,6 +2457,312 @@
         <v>119</v>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" s="2">
+        <v>46224.34672042824</v>
+      </c>
+      <c r="B101" s="3">
+        <v>46224.0</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D101" s="4">
+        <v>160.0</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2">
+        <v>46224.346837997684</v>
+      </c>
+      <c r="B102" s="3">
+        <v>46224.0</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D102" s="4">
+        <v>1200.0</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2">
+        <v>46224.348533703705</v>
+      </c>
+      <c r="B103" s="3">
+        <v>46224.0</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D103" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2">
+        <v>46224.34856788194</v>
+      </c>
+      <c r="B104" s="3">
+        <v>46224.0</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D104" s="4">
+        <v>1100.0</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2">
+        <v>46224.348606203705</v>
+      </c>
+      <c r="B105" s="3">
+        <v>46224.0</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D105" s="4">
+        <v>220.0</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2">
+        <v>46224.34863465278</v>
+      </c>
+      <c r="B106" s="3">
+        <v>46224.0</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D106" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2">
+        <v>46224.34865721065</v>
+      </c>
+      <c r="B107" s="3">
+        <v>46224.0</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D107" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2">
+        <v>46224.34868755787</v>
+      </c>
+      <c r="B108" s="3">
+        <v>46224.0</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D108" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2">
+        <v>46224.348736608794</v>
+      </c>
+      <c r="B109" s="3">
+        <v>46224.0</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D109" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2">
+        <v>46224.389971909724</v>
+      </c>
+      <c r="B110" s="3">
+        <v>46224.0</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D110" s="4">
+        <v>500.0</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2">
+        <v>46224.3899990162</v>
+      </c>
+      <c r="B111" s="3">
+        <v>46224.0</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D111" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2">
+        <v>46224.39007417824</v>
+      </c>
+      <c r="B112" s="3">
+        <v>46224.0</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D112" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2">
+        <v>46224.55259348379</v>
+      </c>
+      <c r="B113" s="3">
+        <v>46224.0</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D113" s="4">
+        <v>300.0</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2">
+        <v>46224.55264100694</v>
+      </c>
+      <c r="B114" s="3">
+        <v>46224.0</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D114" s="4">
+        <v>100.0</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2">
+        <v>46224.55486512731</v>
+      </c>
+      <c r="B115" s="3">
+        <v>46224.0</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D115" s="4">
+        <v>21.0</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2">
+        <v>46224.77226398148</v>
+      </c>
+      <c r="B116" s="3">
+        <v>46224.0</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D116" s="4">
+        <v>150.0</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2">
+        <v>46224.772311493056</v>
+      </c>
+      <c r="B117" s="3">
+        <v>46224.0</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D117" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2">
+        <v>46224.865057523144</v>
+      </c>
+      <c r="B118" s="3">
+        <v>46224.0</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D118" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -2424,10 +2784,10 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2">
@@ -2438,7 +2798,7 @@
         <v>2382681.0</v>
       </c>
       <c r="C2" s="4">
-        <v>9980.0</v>
+        <v>11180.0</v>
       </c>
     </row>
     <row r="3">
@@ -2449,7 +2809,7 @@
         <v>2778093.0</v>
       </c>
       <c r="C3" s="4">
-        <v>3370.0</v>
+        <v>3870.0</v>
       </c>
     </row>
     <row r="4">
@@ -2460,7 +2820,7 @@
         <v>158521.0</v>
       </c>
       <c r="C4" s="4">
-        <v>1700.0</v>
+        <v>2000.0</v>
       </c>
     </row>
     <row r="5">
@@ -2471,7 +2831,7 @@
         <v>169321.0</v>
       </c>
       <c r="C5" s="4">
-        <v>990.0</v>
+        <v>1210.0</v>
       </c>
     </row>
     <row r="6">
@@ -2482,7 +2842,7 @@
         <v>5820554.0</v>
       </c>
       <c r="C6" s="4">
-        <v>660.0</v>
+        <v>770.0</v>
       </c>
     </row>
     <row r="7">
@@ -2493,7 +2853,7 @@
         <v>1425700.0</v>
       </c>
       <c r="C7" s="4">
-        <v>1430.0</v>
+        <v>1540.0</v>
       </c>
     </row>
     <row r="8">
@@ -2504,7 +2864,7 @@
         <v>890948.0</v>
       </c>
       <c r="C8" s="4">
-        <v>660.0</v>
+        <v>770.0</v>
       </c>
     </row>
     <row r="9">
@@ -2515,7 +2875,7 @@
         <v>552569.0</v>
       </c>
       <c r="C9" s="4">
-        <v>660.0</v>
+        <v>770.0</v>
       </c>
     </row>
     <row r="10">
@@ -2526,7 +2886,7 @@
         <v>139781.0</v>
       </c>
       <c r="C10" s="4">
-        <v>598.0</v>
+        <v>708.0</v>
       </c>
     </row>
     <row r="11">
@@ -2537,7 +2897,7 @@
         <v>9031.0</v>
       </c>
       <c r="C11" s="4">
-        <v>126.0</v>
+        <v>147.0</v>
       </c>
     </row>
     <row r="12">
@@ -2548,7 +2908,7 @@
         <v>1123250.0</v>
       </c>
       <c r="C12" s="4">
-        <v>6600.0</v>
+        <v>7700.0</v>
       </c>
     </row>
     <row r="13">
@@ -2559,7 +2919,7 @@
         <v>1832.0</v>
       </c>
       <c r="C13" s="4">
-        <v>14.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="14">
@@ -2570,7 +2930,7 @@
         <v>8100.0</v>
       </c>
       <c r="C14" s="4">
-        <v>550.0</v>
+        <v>650.0</v>
       </c>
     </row>
     <row r="15">
@@ -2581,7 +2941,7 @@
         <v>639.0</v>
       </c>
       <c r="C15" s="4">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="16">
@@ -2592,7 +2952,7 @@
         <v>219463.0</v>
       </c>
       <c r="C16" s="4">
-        <v>660.0</v>
+        <v>770.0</v>
       </c>
     </row>
     <row r="17">
@@ -2603,7 +2963,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" s="4">
-        <v>1630.0</v>
+        <v>2050.0</v>
       </c>
     </row>
   </sheetData>
@@ -2626,19 +2986,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2">
@@ -2655,7 +3015,7 @@
         <v>100.0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3">
@@ -2672,7 +3032,7 @@
         <v>1000.0</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4">
@@ -2689,7 +3049,7 @@
         <v>1.0</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5">
@@ -2706,7 +3066,7 @@
         <v>100.0</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6">
@@ -2723,7 +3083,7 @@
         <v>10.0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7">
@@ -2740,7 +3100,7 @@
         <v>10.0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8">
@@ -2757,7 +3117,7 @@
         <v>10.0</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9">
@@ -2774,7 +3134,7 @@
         <v>100.0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10">
@@ -2791,7 +3151,7 @@
         <v>100.0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11">
@@ -2808,7 +3168,7 @@
         <v>100.0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12">
@@ -2825,7 +3185,7 @@
         <v>100.0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13">
@@ -2876,7 +3236,7 @@
         <v>1.0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16">
@@ -2893,7 +3253,7 @@
         <v>10.0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17">
@@ -2910,7 +3270,7 @@
         <v>7.0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/backup/mantra-records.xlsx
+++ b/backup/mantra-records.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="168">
   <si>
     <t>时间戳</t>
   </si>
@@ -427,6 +427,63 @@
   </si>
   <si>
     <t>mruj2cq2-u3vmol</t>
+  </si>
+  <si>
+    <t>mrv9eosv-4ausj5</t>
+  </si>
+  <si>
+    <t>mrv9evgf-rghb8d</t>
+  </si>
+  <si>
+    <t>mrv9izn3-rskt6e</t>
+  </si>
+  <si>
+    <t>mrv9j205-q5ni0b</t>
+  </si>
+  <si>
+    <t>mrv9j3vj-us83t1</t>
+  </si>
+  <si>
+    <t>mrv9j5o6-h1ml3d</t>
+  </si>
+  <si>
+    <t>mrv9j75t-54uxvr</t>
+  </si>
+  <si>
+    <t>mrv9j8yw-3uwkl2</t>
+  </si>
+  <si>
+    <t>mrv9jca4-4tj9lf</t>
+  </si>
+  <si>
+    <t>mrv9jptg-k0i018</t>
+  </si>
+  <si>
+    <t>mrv9jts0-2yybw3</t>
+  </si>
+  <si>
+    <t>mrvix5tz-thrmlz</t>
+  </si>
+  <si>
+    <t>mrvjclyu-w1nyf6</t>
+  </si>
+  <si>
+    <t>mrvjtev8-4u0pg7</t>
+  </si>
+  <si>
+    <t>mrvpwaj8-xbcoah</t>
+  </si>
+  <si>
+    <t>mrvq95lc-dmobx8</t>
+  </si>
+  <si>
+    <t>mrvqyt97-mo30iu</t>
+  </si>
+  <si>
+    <t>mrvtj0ax-xzbson</t>
+  </si>
+  <si>
+    <t>mrvvzvc2-ma4nox</t>
   </si>
   <si>
     <t>历史基数</t>
@@ -2763,6 +2820,329 @@
         <v>137</v>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" s="2">
+        <v>46225.37715869213</v>
+      </c>
+      <c r="B119" s="3">
+        <v>46225.0</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D119" s="4">
+        <v>180.0</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2">
+        <v>46225.377258506946</v>
+      </c>
+      <c r="B120" s="3">
+        <v>46225.0</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D120" s="4">
+        <v>1200.0</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2">
+        <v>46225.37948128472</v>
+      </c>
+      <c r="B121" s="3">
+        <v>46225.0</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D121" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2">
+        <v>46225.37951672454</v>
+      </c>
+      <c r="B122" s="3">
+        <v>46225.0</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D122" s="4">
+        <v>1100.0</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2">
+        <v>46225.37954480324</v>
+      </c>
+      <c r="B123" s="3">
+        <v>46225.0</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D123" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2">
+        <v>46225.379571736106</v>
+      </c>
+      <c r="B124" s="3">
+        <v>46225.0</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D124" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2">
+        <v>46225.37959408565</v>
+      </c>
+      <c r="B125" s="3">
+        <v>46225.0</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D125" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2">
+        <v>46225.379621203705</v>
+      </c>
+      <c r="B126" s="3">
+        <v>46225.0</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D126" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2">
+        <v>46225.37967087963</v>
+      </c>
+      <c r="B127" s="3">
+        <v>46225.0</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D127" s="4">
+        <v>500.0</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2">
+        <v>46225.379873935184</v>
+      </c>
+      <c r="B128" s="3">
+        <v>46225.0</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D128" s="4">
+        <v>95.0</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2">
+        <v>46225.37993333333</v>
+      </c>
+      <c r="B129" s="3">
+        <v>46225.0</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D129" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2">
+        <v>46225.56209415509</v>
+      </c>
+      <c r="B130" s="3">
+        <v>46225.0</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D130" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2">
+        <v>46225.570436180555</v>
+      </c>
+      <c r="B131" s="3">
+        <v>46225.0</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D131" s="4">
+        <v>200.0</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2">
+        <v>46225.579509675925</v>
+      </c>
+      <c r="B132" s="3">
+        <v>46225.0</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D132" s="4">
+        <v>50.0</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2">
+        <v>46225.69770467593</v>
+      </c>
+      <c r="B133" s="3">
+        <v>46225.0</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D133" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2">
+        <v>46225.704650555555</v>
+      </c>
+      <c r="B134" s="3">
+        <v>46225.0</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D134" s="4">
+        <v>50.0</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2">
+        <v>46225.71850549769</v>
+      </c>
+      <c r="B135" s="3">
+        <v>46225.0</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D135" s="4">
+        <v>21.0</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2">
+        <v>46225.76829121528</v>
+      </c>
+      <c r="B136" s="3">
+        <v>46225.0</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D136" s="4">
+        <v>189.0</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2">
+        <v>46225.81627668982</v>
+      </c>
+      <c r="B137" s="3">
+        <v>46225.0</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D137" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -2784,10 +3164,10 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2">
@@ -2798,7 +3178,7 @@
         <v>2382681.0</v>
       </c>
       <c r="C2" s="4">
-        <v>11180.0</v>
+        <v>12380.0</v>
       </c>
     </row>
     <row r="3">
@@ -2809,7 +3189,7 @@
         <v>2778093.0</v>
       </c>
       <c r="C3" s="4">
-        <v>3870.0</v>
+        <v>4370.0</v>
       </c>
     </row>
     <row r="4">
@@ -2820,7 +3200,7 @@
         <v>158521.0</v>
       </c>
       <c r="C4" s="4">
-        <v>2000.0</v>
+        <v>2200.0</v>
       </c>
     </row>
     <row r="5">
@@ -2831,7 +3211,7 @@
         <v>169321.0</v>
       </c>
       <c r="C5" s="4">
-        <v>1210.0</v>
+        <v>1320.0</v>
       </c>
     </row>
     <row r="6">
@@ -2842,7 +3222,7 @@
         <v>5820554.0</v>
       </c>
       <c r="C6" s="4">
-        <v>770.0</v>
+        <v>880.0</v>
       </c>
     </row>
     <row r="7">
@@ -2853,7 +3233,7 @@
         <v>1425700.0</v>
       </c>
       <c r="C7" s="4">
-        <v>1540.0</v>
+        <v>1650.0</v>
       </c>
     </row>
     <row r="8">
@@ -2864,7 +3244,7 @@
         <v>890948.0</v>
       </c>
       <c r="C8" s="4">
-        <v>770.0</v>
+        <v>880.0</v>
       </c>
     </row>
     <row r="9">
@@ -2875,7 +3255,7 @@
         <v>552569.0</v>
       </c>
       <c r="C9" s="4">
-        <v>770.0</v>
+        <v>880.0</v>
       </c>
     </row>
     <row r="10">
@@ -2886,7 +3266,7 @@
         <v>139781.0</v>
       </c>
       <c r="C10" s="4">
-        <v>708.0</v>
+        <v>803.0</v>
       </c>
     </row>
     <row r="11">
@@ -2897,7 +3277,7 @@
         <v>9031.0</v>
       </c>
       <c r="C11" s="4">
-        <v>147.0</v>
+        <v>168.0</v>
       </c>
     </row>
     <row r="12">
@@ -2908,7 +3288,7 @@
         <v>1123250.0</v>
       </c>
       <c r="C12" s="4">
-        <v>7700.0</v>
+        <v>8800.0</v>
       </c>
     </row>
     <row r="13">
@@ -2919,7 +3299,7 @@
         <v>1832.0</v>
       </c>
       <c r="C13" s="4">
-        <v>19.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="14">
@@ -2930,7 +3310,7 @@
         <v>8100.0</v>
       </c>
       <c r="C14" s="4">
-        <v>650.0</v>
+        <v>750.0</v>
       </c>
     </row>
     <row r="15">
@@ -2941,7 +3321,7 @@
         <v>639.0</v>
       </c>
       <c r="C15" s="4">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="16">
@@ -2952,7 +3332,7 @@
         <v>219463.0</v>
       </c>
       <c r="C16" s="4">
-        <v>770.0</v>
+        <v>880.0</v>
       </c>
     </row>
     <row r="17">
@@ -2963,7 +3343,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" s="4">
-        <v>2050.0</v>
+        <v>2529.0</v>
       </c>
     </row>
   </sheetData>
@@ -2986,19 +3366,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2">
@@ -3015,7 +3395,7 @@
         <v>100.0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3">
@@ -3032,7 +3412,7 @@
         <v>1000.0</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4">
@@ -3049,7 +3429,7 @@
         <v>1.0</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5">
@@ -3066,7 +3446,7 @@
         <v>100.0</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6">
@@ -3083,7 +3463,7 @@
         <v>10.0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7">
@@ -3100,7 +3480,7 @@
         <v>10.0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8">
@@ -3117,7 +3497,7 @@
         <v>10.0</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9">
@@ -3134,7 +3514,7 @@
         <v>100.0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10">
@@ -3151,7 +3531,7 @@
         <v>100.0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -3168,7 +3548,7 @@
         <v>100.0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12">
@@ -3185,7 +3565,7 @@
         <v>100.0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -3236,7 +3616,7 @@
         <v>1.0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
     </row>
     <row r="16">
@@ -3253,7 +3633,7 @@
         <v>10.0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17">
@@ -3270,7 +3650,7 @@
         <v>7.0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/backup/mantra-records.xlsx
+++ b/backup/mantra-records.xlsx
@@ -13,110 +13,146 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="184">
   <si>
     <t>时间戳</t>
   </si>
   <si>
+    <t>类别名称</t>
+  </si>
+  <si>
+    <t>类别</t>
+  </si>
+  <si>
     <t>日期</t>
   </si>
   <si>
-    <t>类别</t>
+    <t>快捷按钮1</t>
+  </si>
+  <si>
+    <t>历史基数</t>
+  </si>
+  <si>
+    <t>快捷按钮2</t>
+  </si>
+  <si>
+    <t>应用累计</t>
   </si>
   <si>
     <t>数量</t>
   </si>
   <si>
+    <t>快捷按钮3</t>
+  </si>
+  <si>
     <t>记录ID</t>
   </si>
   <si>
     <t>莲师心咒</t>
   </si>
   <si>
+    <t>组别</t>
+  </si>
+  <si>
+    <t>金刚桥外皈依</t>
+  </si>
+  <si>
+    <t>金刚桥</t>
+  </si>
+  <si>
     <t>mrlks9td-k4uqs3</t>
   </si>
   <si>
     <t>绿度母心咒</t>
   </si>
   <si>
+    <t>心咒</t>
+  </si>
+  <si>
     <t>mrlksetf-hs5dn5</t>
   </si>
   <si>
     <t>普巴金刚心咒</t>
   </si>
   <si>
+    <t>邬金空行</t>
+  </si>
+  <si>
     <t>mrlkt29s-qamx95</t>
   </si>
   <si>
     <t>地藏心咒</t>
   </si>
   <si>
+    <t>地藏圣号</t>
+  </si>
+  <si>
+    <t>圣号与礼赞</t>
+  </si>
+  <si>
+    <t>观音心咒</t>
+  </si>
+  <si>
     <t>mrlkt5q5-bxqyk5</t>
   </si>
   <si>
-    <t>观音心咒</t>
+    <t>莲花作明佛母亲近咒</t>
   </si>
   <si>
     <t>mrlkt9ek-k7mk8m</t>
   </si>
   <si>
-    <t>莲花作明佛母亲近咒</t>
+    <t>文殊心咒</t>
+  </si>
+  <si>
+    <t>黑财神心咒</t>
   </si>
   <si>
     <t>mrlktc1w-fikhnq</t>
   </si>
   <si>
-    <t>文殊心咒</t>
+    <t>百字明</t>
+  </si>
+  <si>
+    <t>金刚萨埵黑鲁噶百字明</t>
   </si>
   <si>
     <t>mrlktf0r-4v8u9r</t>
   </si>
   <si>
-    <t>百字明</t>
+    <t>21度母礼赞</t>
   </si>
   <si>
     <t>mrlktosu-qse7qm</t>
   </si>
   <si>
-    <t>黑财神心咒</t>
+    <t>无死长寿祈祷文</t>
   </si>
   <si>
     <t>mrlktwjm-kbj6wb</t>
   </si>
   <si>
-    <t>地藏圣号</t>
+    <t>扎嘉传承</t>
   </si>
   <si>
     <t>mrlku0wu-exoemt</t>
   </si>
   <si>
-    <t>扎嘉传承</t>
-  </si>
-  <si>
     <t>mrlkuhbk-soifop</t>
   </si>
   <si>
-    <t>邬金空行</t>
+    <t>祈祷与传承</t>
   </si>
   <si>
     <t>mrlkupum-xofrni</t>
   </si>
   <si>
-    <t>无死长寿祈祷文</t>
-  </si>
-  <si>
     <t>mrlkwmw2-uc5ph7</t>
   </si>
   <si>
-    <t>金刚萨埵黑鲁噶百字明</t>
-  </si>
-  <si>
     <t>mrlz5h2o-5eid4e</t>
   </si>
   <si>
-    <t>21度母礼赞</t>
-  </si>
-  <si>
     <t>mrlz63f3-hptnt4</t>
   </si>
   <si>
@@ -165,9 +201,6 @@
     <t>mrmzbuii-wqptl2</t>
   </si>
   <si>
-    <t>金刚桥外皈依</t>
-  </si>
-  <si>
     <t>mro5099x-4w4wei</t>
   </si>
   <si>
@@ -486,37 +519,52 @@
     <t>mrvvzvc2-ma4nox</t>
   </si>
   <si>
-    <t>历史基数</t>
-  </si>
-  <si>
-    <t>应用累计</t>
-  </si>
-  <si>
-    <t>类别名称</t>
-  </si>
-  <si>
-    <t>快捷按钮1</t>
-  </si>
-  <si>
-    <t>快捷按钮2</t>
-  </si>
-  <si>
-    <t>快捷按钮3</t>
-  </si>
-  <si>
-    <t>组别</t>
-  </si>
-  <si>
-    <t>金刚桥</t>
-  </si>
-  <si>
-    <t>心咒</t>
-  </si>
-  <si>
-    <t>圣号与礼赞</t>
-  </si>
-  <si>
-    <t>祈祷与传承</t>
+    <t>mrwmc93b-14itxx</t>
+  </si>
+  <si>
+    <t>mrwmccwb-mjv773</t>
+  </si>
+  <si>
+    <t>mrwomv7f-wjochq</t>
+  </si>
+  <si>
+    <t>mrwomxeu-tj9q8l</t>
+  </si>
+  <si>
+    <t>mrwon0dh-94y6od</t>
+  </si>
+  <si>
+    <t>mrwon1pp-tdzv8f</t>
+  </si>
+  <si>
+    <t>mrwon3zs-rt6hlq</t>
+  </si>
+  <si>
+    <t>mrwon7ay-uned4o</t>
+  </si>
+  <si>
+    <t>mrwonbo4-tt7t8o</t>
+  </si>
+  <si>
+    <t>mrwonej8-bwudtb</t>
+  </si>
+  <si>
+    <t>mrwwt5ye-st02qv</t>
+  </si>
+  <si>
+    <t>mrwwt89r-07fgoy</t>
+  </si>
+  <si>
+    <t>mrwxczlo-t2fevy</t>
+  </si>
+  <si>
+    <t>mrx0ti0c-bi2fws</t>
+  </si>
+  <si>
+    <t>mrx8n0du-z1vykw</t>
+  </si>
+  <si>
+    <t>mrx8rbuy-ex1nqu</t>
   </si>
 </sst>
 </file>
@@ -573,14 +621,14 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="14" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -819,2328 +867,2600 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
         <v>46218.59993390046</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="4">
         <v>46218.0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="4">
+        <v>11</v>
+      </c>
+      <c r="D2" s="5">
         <v>2200.0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2">
         <v>46218.60000892361</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="4">
         <v>46218.0</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="4">
+        <v>16</v>
+      </c>
+      <c r="D3" s="5">
         <v>500.0</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2">
         <v>46218.60036074074</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="4">
         <v>46218.0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="4">
+        <v>19</v>
+      </c>
+      <c r="D4" s="5">
         <v>330.0</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2">
         <v>46218.60041255787</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="4">
         <v>46218.0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="4">
+        <v>22</v>
+      </c>
+      <c r="D5" s="5">
         <v>220.0</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2">
         <v>46218.60046773148</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="4">
         <v>46218.0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="4">
+        <v>25</v>
+      </c>
+      <c r="D6" s="5">
         <v>110.0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2">
         <v>46218.60050746528</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="4">
         <v>46218.0</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="4">
+        <v>27</v>
+      </c>
+      <c r="D7" s="5">
         <v>110.0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2">
         <v>46218.600551979165</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="4">
         <v>46218.0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="4">
+        <v>29</v>
+      </c>
+      <c r="D8" s="5">
         <v>110.0</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2">
         <v>46218.60069868056</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="4">
         <v>46218.0</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="4">
+        <v>32</v>
+      </c>
+      <c r="D9" s="5">
         <v>90.0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2">
         <v>46218.60081484954</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="4">
         <v>46218.0</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="4">
+        <v>30</v>
+      </c>
+      <c r="D10" s="5">
         <v>110.0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2">
         <v>46218.60088034722</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="4">
         <v>46218.0</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="5">
         <v>1100.0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2">
         <v>46218.60112648148</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="4">
         <v>46218.0</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="4">
+        <v>39</v>
+      </c>
+      <c r="D12" s="5">
         <v>1.0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2">
         <v>46218.6012544213</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="4">
         <v>46218.0</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="4">
+        <v>20</v>
+      </c>
+      <c r="D13" s="5">
         <v>110.0</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2">
         <v>46218.60229002315</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="4">
         <v>46218.0</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="4">
+        <v>37</v>
+      </c>
+      <c r="D14" s="5">
         <v>50.0</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2">
         <v>46218.879222777774</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="4">
         <v>46218.0</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" s="4">
+        <v>33</v>
+      </c>
+      <c r="D15" s="5">
         <v>21.0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2">
         <v>46218.87955795139</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="4">
         <v>46218.0</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="4">
+        <v>35</v>
+      </c>
+      <c r="D16" s="5">
         <v>1.0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2">
         <v>46219.36083100694</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="4">
         <v>46219.0</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D17" s="4">
+        <v>11</v>
+      </c>
+      <c r="D17" s="5">
         <v>2200.0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2">
         <v>46219.36095940972</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="4">
         <v>46219.0</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" s="4">
+        <v>22</v>
+      </c>
+      <c r="D18" s="5">
         <v>220.0</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2">
         <v>46219.36098726852</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="4">
         <v>46219.0</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="4">
+        <v>25</v>
+      </c>
+      <c r="D19" s="5">
         <v>110.0</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2">
         <v>46219.36102891204</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="4">
         <v>46219.0</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" s="4">
+        <v>29</v>
+      </c>
+      <c r="D20" s="5">
         <v>110.0</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2">
         <v>46219.361140196765</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="4">
         <v>46219.0</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="4">
+        <v>30</v>
+      </c>
+      <c r="D21" s="5">
         <v>110.0</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2">
         <v>46219.36120090278</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="4">
         <v>46219.0</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="5">
         <v>1100.0</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2">
         <v>46219.361246134256</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="4">
         <v>46219.0</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D23" s="4">
+        <v>39</v>
+      </c>
+      <c r="D23" s="5">
         <v>1.0</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2">
         <v>46219.36128604166</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="4">
         <v>46219.0</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D24" s="4">
+        <v>20</v>
+      </c>
+      <c r="D24" s="5">
         <v>110.0</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2">
         <v>46219.36148746528</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="4">
         <v>46219.0</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" s="4">
+        <v>32</v>
+      </c>
+      <c r="D25" s="5">
         <v>90.0</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2">
         <v>46219.37500490741</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="4">
         <v>46219.0</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D26" s="4">
+        <v>16</v>
+      </c>
+      <c r="D26" s="5">
         <v>500.0</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2">
         <v>46219.378031932865</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="4">
         <v>46219.0</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D27" s="4">
+        <v>27</v>
+      </c>
+      <c r="D27" s="5">
         <v>110.0</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2">
         <v>46219.53696891204</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="4">
         <v>46219.0</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D28" s="4">
+        <v>35</v>
+      </c>
+      <c r="D28" s="5">
         <v>3.0</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2">
         <v>46219.57221748843</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="4">
         <v>46219.0</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="4">
+        <v>19</v>
+      </c>
+      <c r="D29" s="5">
         <v>300.0</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2">
         <v>46219.572925706016</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="4">
         <v>46219.0</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D30" s="4">
+        <v>33</v>
+      </c>
+      <c r="D30" s="5">
         <v>21.0</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2">
         <v>46219.582504375</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B31" s="4">
         <v>46219.0</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D31" s="4">
+        <v>37</v>
+      </c>
+      <c r="D31" s="5">
         <v>100.0</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2">
         <v>46220.39272579861</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="4">
         <v>46220.0</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D32" s="4">
+        <v>13</v>
+      </c>
+      <c r="D32" s="5">
         <v>330.0</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2">
         <v>46220.39278981481</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B33" s="4">
         <v>46220.0</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D33" s="4">
+        <v>11</v>
+      </c>
+      <c r="D33" s="5">
         <v>330.0</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2">
         <v>46220.392932083334</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B34" s="4">
         <v>46220.0</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D34" s="5">
         <v>1100.0</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2">
         <v>46220.392972974536</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B35" s="4">
         <v>46220.0</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D35" s="4">
+        <v>22</v>
+      </c>
+      <c r="D35" s="5">
         <v>110.0</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2">
         <v>46220.39300672454</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B36" s="4">
         <v>46220.0</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D36" s="4">
+        <v>25</v>
+      </c>
+      <c r="D36" s="5">
         <v>110.0</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2">
         <v>46220.393032708336</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B37" s="4">
         <v>46220.0</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D37" s="4">
+        <v>29</v>
+      </c>
+      <c r="D37" s="5">
         <v>110.0</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2">
         <v>46220.39306212963</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B38" s="4">
         <v>46220.0</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D38" s="4">
+        <v>30</v>
+      </c>
+      <c r="D38" s="5">
         <v>110.0</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2">
         <v>46220.39315246527</v>
       </c>
-      <c r="B39" s="3">
+      <c r="B39" s="4">
         <v>46220.0</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D39" s="4">
+        <v>16</v>
+      </c>
+      <c r="D39" s="5">
         <v>500.0</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2">
         <v>46220.3932059375</v>
       </c>
-      <c r="B40" s="3">
+      <c r="B40" s="4">
         <v>46220.0</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D40" s="4">
+        <v>27</v>
+      </c>
+      <c r="D40" s="5">
         <v>110.0</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2">
         <v>46220.39326859954</v>
       </c>
-      <c r="B41" s="3">
+      <c r="B41" s="4">
         <v>46220.0</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D41" s="4">
+        <v>32</v>
+      </c>
+      <c r="D41" s="5">
         <v>90.0</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2">
         <v>46220.39332800926</v>
       </c>
-      <c r="B42" s="3">
+      <c r="B42" s="4">
         <v>46220.0</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D42" s="4">
+        <v>39</v>
+      </c>
+      <c r="D42" s="5">
         <v>1.0</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2">
         <v>46220.53172856482</v>
       </c>
-      <c r="B43" s="3">
+      <c r="B43" s="4">
         <v>46220.0</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D43" s="4">
+        <v>11</v>
+      </c>
+      <c r="D43" s="5">
         <v>500.0</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2">
         <v>46220.53914545139</v>
       </c>
-      <c r="B44" s="3">
+      <c r="B44" s="4">
         <v>46220.0</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D44" s="4">
+        <v>11</v>
+      </c>
+      <c r="D44" s="5">
         <v>350.0</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2">
         <v>46220.56417989584</v>
       </c>
-      <c r="B45" s="3">
+      <c r="B45" s="4">
         <v>46220.0</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="4">
+        <v>19</v>
+      </c>
+      <c r="D45" s="5">
         <v>300.0</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2">
         <v>46220.566308622685</v>
       </c>
-      <c r="B46" s="3">
+      <c r="B46" s="4">
         <v>46220.0</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D46" s="4">
+        <v>35</v>
+      </c>
+      <c r="D46" s="5">
         <v>3.0</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2">
         <v>46220.60263800926</v>
       </c>
-      <c r="B47" s="3">
+      <c r="B47" s="4">
         <v>46220.0</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D47" s="4">
+        <v>37</v>
+      </c>
+      <c r="D47" s="5">
         <v>100.0</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2">
         <v>46220.61828956018</v>
       </c>
-      <c r="B48" s="3">
+      <c r="B48" s="4">
         <v>46220.0</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D48" s="4">
+        <v>33</v>
+      </c>
+      <c r="D48" s="5">
         <v>21.0</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2">
         <v>46220.78008434028</v>
       </c>
-      <c r="B49" s="3">
+      <c r="B49" s="4">
         <v>46220.0</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D49" s="4">
+        <v>13</v>
+      </c>
+      <c r="D49" s="5">
         <v>100.0</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2">
         <v>46220.9643725</v>
       </c>
-      <c r="B50" s="3">
+      <c r="B50" s="4">
         <v>46220.0</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D50" s="4">
+        <v>20</v>
+      </c>
+      <c r="D50" s="5">
         <v>110.0</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2">
         <v>46221.481308622686</v>
       </c>
-      <c r="B51" s="3">
+      <c r="B51" s="4">
         <v>46221.0</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D51" s="4">
+        <v>13</v>
+      </c>
+      <c r="D51" s="5">
         <v>350.0</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2">
         <v>46221.481428680556</v>
       </c>
-      <c r="B52" s="3">
+      <c r="B52" s="4">
         <v>46221.0</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D52" s="4">
+        <v>32</v>
+      </c>
+      <c r="D52" s="5">
         <v>110.0</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2">
         <v>46221.52650024305</v>
       </c>
-      <c r="B53" s="3">
+      <c r="B53" s="4">
         <v>46221.0</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D53" s="4">
+        <v>11</v>
+      </c>
+      <c r="D53" s="5">
         <v>2200.0</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2">
         <v>46221.52749582176</v>
       </c>
-      <c r="B54" s="3">
+      <c r="B54" s="4">
         <v>46221.0</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D54" s="4">
+        <v>20</v>
+      </c>
+      <c r="D54" s="5">
         <v>110.0</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2">
         <v>46221.52754980324</v>
       </c>
-      <c r="B55" s="3">
+      <c r="B55" s="4">
         <v>46221.0</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D55" s="4">
+        <v>25</v>
+      </c>
+      <c r="D55" s="5">
         <v>110.0</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2">
         <v>46221.527581296294</v>
       </c>
-      <c r="B56" s="3">
+      <c r="B56" s="4">
         <v>46221.0</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D56" s="4">
+        <v>29</v>
+      </c>
+      <c r="D56" s="5">
         <v>110.0</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2">
         <v>46221.527755613424</v>
       </c>
-      <c r="B57" s="3">
+      <c r="B57" s="4">
         <v>46221.0</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D57" s="4">
+        <v>30</v>
+      </c>
+      <c r="D57" s="5">
         <v>110.0</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2">
         <v>46221.52786003472</v>
       </c>
-      <c r="B58" s="3">
+      <c r="B58" s="4">
         <v>46221.0</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D58" s="4">
+        <v>39</v>
+      </c>
+      <c r="D58" s="5">
         <v>1.0</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2">
         <v>46221.56208596065</v>
       </c>
-      <c r="B59" s="3">
+      <c r="B59" s="4">
         <v>46221.0</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D59" s="4">
+      <c r="D59" s="5">
         <v>1100.0</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2">
         <v>46221.562139201385</v>
       </c>
-      <c r="B60" s="3">
+      <c r="B60" s="4">
         <v>46221.0</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D60" s="4">
+        <v>22</v>
+      </c>
+      <c r="D60" s="5">
         <v>220.0</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2">
         <v>46221.56227361111</v>
       </c>
-      <c r="B61" s="3">
+      <c r="B61" s="4">
         <v>46221.0</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D61" s="4">
+        <v>16</v>
+      </c>
+      <c r="D61" s="5">
         <v>1100.0</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2">
         <v>46221.59101953704</v>
       </c>
-      <c r="B62" s="3">
+      <c r="B62" s="4">
         <v>46221.0</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D62" s="4">
+        <v>27</v>
+      </c>
+      <c r="D62" s="5">
         <v>880.0</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2">
         <v>46221.59110706019</v>
       </c>
-      <c r="B63" s="3">
+      <c r="B63" s="4">
         <v>46221.0</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D63" s="4">
+        <v>37</v>
+      </c>
+      <c r="D63" s="5">
         <v>100.0</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2">
         <v>46221.591245868054</v>
       </c>
-      <c r="B64" s="3">
+      <c r="B64" s="4">
         <v>46221.0</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D64" s="4">
+        <v>35</v>
+      </c>
+      <c r="D64" s="5">
         <v>5.0</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2">
         <v>46221.59138636574</v>
       </c>
-      <c r="B65" s="3">
+      <c r="B65" s="4">
         <v>46221.0</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D65" s="4">
+        <v>19</v>
+      </c>
+      <c r="D65" s="5">
         <v>330.0</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2">
         <v>46221.5952940625</v>
       </c>
-      <c r="B66" s="3">
+      <c r="B66" s="4">
         <v>46221.0</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D66" s="4">
+        <v>33</v>
+      </c>
+      <c r="D66" s="5">
         <v>21.0</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2">
         <v>46222.55562850695</v>
       </c>
-      <c r="B67" s="3">
+      <c r="B67" s="4">
         <v>46222.0</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D67" s="4">
+        <v>13</v>
+      </c>
+      <c r="D67" s="5">
         <v>300.0</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2">
         <v>46222.555725659724</v>
       </c>
-      <c r="B68" s="3">
+      <c r="B68" s="4">
         <v>46222.0</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D68" s="4">
+        <v>11</v>
+      </c>
+      <c r="D68" s="5">
         <v>1100.0</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2">
         <v>46222.555776423615</v>
       </c>
-      <c r="B69" s="3">
+      <c r="B69" s="4">
         <v>46222.0</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D69" s="4">
+        <v>25</v>
+      </c>
+      <c r="D69" s="5">
         <v>110.0</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2">
         <v>46222.55580371528</v>
       </c>
-      <c r="B70" s="3">
+      <c r="B70" s="4">
         <v>46222.0</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D70" s="4">
+        <v>29</v>
+      </c>
+      <c r="D70" s="5">
         <v>110.0</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2">
         <v>46222.55584842592</v>
       </c>
-      <c r="B71" s="3">
+      <c r="B71" s="4">
         <v>46222.0</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D71" s="4">
+        <v>30</v>
+      </c>
+      <c r="D71" s="5">
         <v>110.0</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2">
         <v>46222.55593107639</v>
       </c>
-      <c r="B72" s="3">
+      <c r="B72" s="4">
         <v>46222.0</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D72" s="4">
+        <v>39</v>
+      </c>
+      <c r="D72" s="5">
         <v>1.0</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2">
         <v>46222.566782037036</v>
       </c>
-      <c r="B73" s="3">
+      <c r="B73" s="4">
         <v>46222.0</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D73" s="4">
+        <v>20</v>
+      </c>
+      <c r="D73" s="5">
         <v>110.0</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2">
         <v>46222.566821898145</v>
       </c>
-      <c r="B74" s="3">
+      <c r="B74" s="4">
         <v>46222.0</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D74" s="4">
+      <c r="D74" s="5">
         <v>1100.0</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2">
         <v>46222.566868657406</v>
       </c>
-      <c r="B75" s="3">
+      <c r="B75" s="4">
         <v>46222.0</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D75" s="4">
+        <v>22</v>
+      </c>
+      <c r="D75" s="5">
         <v>110.0</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2">
         <v>46222.56694369213</v>
       </c>
-      <c r="B76" s="3">
+      <c r="B76" s="4">
         <v>46222.0</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D76" s="4">
+        <v>16</v>
+      </c>
+      <c r="D76" s="5">
         <v>110.0</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2">
         <v>46222.56698377315</v>
       </c>
-      <c r="B77" s="3">
+      <c r="B77" s="4">
         <v>46222.0</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D77" s="4">
+        <v>27</v>
+      </c>
+      <c r="D77" s="5">
         <v>110.0</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2">
         <v>46222.5670393287</v>
       </c>
-      <c r="B78" s="3">
+      <c r="B78" s="4">
         <v>46222.0</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D78" s="4">
+        <v>35</v>
+      </c>
+      <c r="D78" s="5">
         <v>1.0</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2">
         <v>46222.667202881945</v>
       </c>
-      <c r="B79" s="3">
+      <c r="B79" s="4">
         <v>46222.0</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D79" s="4">
+        <v>19</v>
+      </c>
+      <c r="D79" s="5">
         <v>110.0</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2">
         <v>46222.676215150466</v>
       </c>
-      <c r="B80" s="3">
+      <c r="B80" s="4">
         <v>46222.0</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D80" s="4">
+        <v>33</v>
+      </c>
+      <c r="D80" s="5">
         <v>21.0</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2">
         <v>46222.89222185186</v>
       </c>
-      <c r="B81" s="3">
+      <c r="B81" s="4">
         <v>46222.0</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D81" s="4">
+        <v>13</v>
+      </c>
+      <c r="D81" s="5">
         <v>220.0</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2">
         <v>46222.90832773148</v>
       </c>
-      <c r="B82" s="3">
+      <c r="B82" s="4">
         <v>46222.0</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D82" s="4">
+        <v>32</v>
+      </c>
+      <c r="D82" s="5">
         <v>108.0</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2">
         <v>46222.917884560185</v>
       </c>
-      <c r="B83" s="3">
+      <c r="B83" s="4">
         <v>46222.0</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D83" s="4">
+        <v>37</v>
+      </c>
+      <c r="D83" s="5">
         <v>100.0</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2">
         <v>46223.35147047453</v>
       </c>
-      <c r="B84" s="3">
+      <c r="B84" s="4">
         <v>46223.0</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D84" s="4">
+        <v>13</v>
+      </c>
+      <c r="D84" s="5">
         <v>330.0</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2">
         <v>46223.39655936343</v>
       </c>
-      <c r="B85" s="3">
+      <c r="B85" s="4">
         <v>46223.0</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D85" s="4">
+        <v>32</v>
+      </c>
+      <c r="D85" s="5">
         <v>110.0</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2">
         <v>46223.41721368056</v>
       </c>
-      <c r="B86" s="3">
+      <c r="B86" s="4">
         <v>46223.0</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D86" s="4">
+        <v>11</v>
+      </c>
+      <c r="D86" s="5">
         <v>1100.0</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2">
         <v>46223.41724953704</v>
       </c>
-      <c r="B87" s="3">
+      <c r="B87" s="4">
         <v>46223.0</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D87" s="4">
+        <v>20</v>
+      </c>
+      <c r="D87" s="5">
         <v>110.0</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2">
         <v>46223.41730127315</v>
       </c>
-      <c r="B88" s="3">
+      <c r="B88" s="4">
         <v>46223.0</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D88" s="4">
+        <v>25</v>
+      </c>
+      <c r="D88" s="5">
         <v>110.0</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2">
         <v>46223.41733108796</v>
       </c>
-      <c r="B89" s="3">
+      <c r="B89" s="4">
         <v>46223.0</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D89" s="4">
+        <v>29</v>
+      </c>
+      <c r="D89" s="5">
         <v>110.0</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2">
         <v>46223.417364733796</v>
       </c>
-      <c r="B90" s="3">
+      <c r="B90" s="4">
         <v>46223.0</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D90" s="4">
+        <v>30</v>
+      </c>
+      <c r="D90" s="5">
         <v>110.0</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2">
         <v>46223.417424976855</v>
       </c>
-      <c r="B91" s="3">
+      <c r="B91" s="4">
         <v>46223.0</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D91" s="4">
+        <v>39</v>
+      </c>
+      <c r="D91" s="5">
         <v>1.0</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2">
         <v>46223.427174247685</v>
       </c>
-      <c r="B92" s="3">
+      <c r="B92" s="4">
         <v>46223.0</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D92" s="4">
+      <c r="D92" s="5">
         <v>1100.0</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2">
         <v>46223.43069275463</v>
       </c>
-      <c r="B93" s="3">
+      <c r="B93" s="4">
         <v>46223.0</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D93" s="4">
+        <v>22</v>
+      </c>
+      <c r="D93" s="5">
         <v>110.0</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2">
         <v>46223.623396574076</v>
       </c>
-      <c r="B94" s="3">
+      <c r="B94" s="4">
         <v>46223.0</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D94" s="4">
+        <v>19</v>
+      </c>
+      <c r="D94" s="5">
         <v>330.0</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2">
         <v>46223.6235443287</v>
       </c>
-      <c r="B95" s="3">
+      <c r="B95" s="4">
         <v>46223.0</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D95" s="4">
+        <v>37</v>
+      </c>
+      <c r="D95" s="5">
         <v>50.0</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2">
         <v>46223.883227592596</v>
       </c>
-      <c r="B96" s="3">
+      <c r="B96" s="4">
         <v>46223.0</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D96" s="4">
+        <v>16</v>
+      </c>
+      <c r="D96" s="5">
         <v>660.0</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2">
         <v>46223.883269224534</v>
       </c>
-      <c r="B97" s="3">
+      <c r="B97" s="4">
         <v>46223.0</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D97" s="4">
+        <v>27</v>
+      </c>
+      <c r="D97" s="5">
         <v>110.0</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2">
         <v>46223.88392460648</v>
       </c>
-      <c r="B98" s="3">
+      <c r="B98" s="4">
         <v>46223.0</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D98" s="4">
+        <v>33</v>
+      </c>
+      <c r="D98" s="5">
         <v>21.0</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2">
         <v>46223.884048865744</v>
       </c>
-      <c r="B99" s="3">
+      <c r="B99" s="4">
         <v>46223.0</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D99" s="4">
+        <v>35</v>
+      </c>
+      <c r="D99" s="5">
         <v>1.0</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2">
         <v>46223.92497723379</v>
       </c>
-      <c r="B100" s="3">
+      <c r="B100" s="4">
         <v>46223.0</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D100" s="4">
+        <v>37</v>
+      </c>
+      <c r="D100" s="5">
         <v>50.0</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2">
         <v>46224.34672042824</v>
       </c>
-      <c r="B101" s="3">
+      <c r="B101" s="4">
         <v>46224.0</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D101" s="4">
+        <v>13</v>
+      </c>
+      <c r="D101" s="5">
         <v>160.0</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2">
         <v>46224.346837997684</v>
       </c>
-      <c r="B102" s="3">
+      <c r="B102" s="4">
         <v>46224.0</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D102" s="4">
+        <v>11</v>
+      </c>
+      <c r="D102" s="5">
         <v>1200.0</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2">
         <v>46224.348533703705</v>
       </c>
-      <c r="B103" s="3">
+      <c r="B103" s="4">
         <v>46224.0</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D103" s="4">
+        <v>20</v>
+      </c>
+      <c r="D103" s="5">
         <v>110.0</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2">
         <v>46224.34856788194</v>
       </c>
-      <c r="B104" s="3">
+      <c r="B104" s="4">
         <v>46224.0</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D104" s="4">
+      <c r="D104" s="5">
         <v>1100.0</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2">
         <v>46224.348606203705</v>
       </c>
-      <c r="B105" s="3">
+      <c r="B105" s="4">
         <v>46224.0</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D105" s="4">
+        <v>22</v>
+      </c>
+      <c r="D105" s="5">
         <v>220.0</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2">
         <v>46224.34863465278</v>
       </c>
-      <c r="B106" s="3">
+      <c r="B106" s="4">
         <v>46224.0</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D106" s="4">
+        <v>25</v>
+      </c>
+      <c r="D106" s="5">
         <v>110.0</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2">
         <v>46224.34865721065</v>
       </c>
-      <c r="B107" s="3">
+      <c r="B107" s="4">
         <v>46224.0</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D107" s="4">
+        <v>29</v>
+      </c>
+      <c r="D107" s="5">
         <v>110.0</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2">
         <v>46224.34868755787</v>
       </c>
-      <c r="B108" s="3">
+      <c r="B108" s="4">
         <v>46224.0</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D108" s="4">
+        <v>30</v>
+      </c>
+      <c r="D108" s="5">
         <v>110.0</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2">
         <v>46224.348736608794</v>
       </c>
-      <c r="B109" s="3">
+      <c r="B109" s="4">
         <v>46224.0</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D109" s="4">
+        <v>39</v>
+      </c>
+      <c r="D109" s="5">
         <v>1.0</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2">
         <v>46224.389971909724</v>
       </c>
-      <c r="B110" s="3">
+      <c r="B110" s="4">
         <v>46224.0</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D110" s="4">
+        <v>16</v>
+      </c>
+      <c r="D110" s="5">
         <v>500.0</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2">
         <v>46224.3899990162</v>
       </c>
-      <c r="B111" s="3">
+      <c r="B111" s="4">
         <v>46224.0</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D111" s="4">
+        <v>27</v>
+      </c>
+      <c r="D111" s="5">
         <v>110.0</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2">
         <v>46224.39007417824</v>
       </c>
-      <c r="B112" s="3">
+      <c r="B112" s="4">
         <v>46224.0</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D112" s="4">
+        <v>32</v>
+      </c>
+      <c r="D112" s="5">
         <v>110.0</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2">
         <v>46224.55259348379</v>
       </c>
-      <c r="B113" s="3">
+      <c r="B113" s="4">
         <v>46224.0</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D113" s="4">
+        <v>19</v>
+      </c>
+      <c r="D113" s="5">
         <v>300.0</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2">
         <v>46224.55264100694</v>
       </c>
-      <c r="B114" s="3">
+      <c r="B114" s="4">
         <v>46224.0</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D114" s="4">
+        <v>37</v>
+      </c>
+      <c r="D114" s="5">
         <v>100.0</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2">
         <v>46224.55486512731</v>
       </c>
-      <c r="B115" s="3">
+      <c r="B115" s="4">
         <v>46224.0</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D115" s="4">
+        <v>33</v>
+      </c>
+      <c r="D115" s="5">
         <v>21.0</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2">
         <v>46224.77226398148</v>
       </c>
-      <c r="B116" s="3">
+      <c r="B116" s="4">
         <v>46224.0</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D116" s="4">
+        <v>13</v>
+      </c>
+      <c r="D116" s="5">
         <v>150.0</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2">
         <v>46224.772311493056</v>
       </c>
-      <c r="B117" s="3">
+      <c r="B117" s="4">
         <v>46224.0</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D117" s="4">
+        <v>35</v>
+      </c>
+      <c r="D117" s="5">
         <v>5.0</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2">
         <v>46224.865057523144</v>
       </c>
-      <c r="B118" s="3">
+      <c r="B118" s="4">
         <v>46224.0</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D118" s="4">
+        <v>13</v>
+      </c>
+      <c r="D118" s="5">
         <v>110.0</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2">
         <v>46225.37715869213</v>
       </c>
-      <c r="B119" s="3">
+      <c r="B119" s="4">
         <v>46225.0</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D119" s="4">
+        <v>13</v>
+      </c>
+      <c r="D119" s="5">
         <v>180.0</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2">
         <v>46225.377258506946</v>
       </c>
-      <c r="B120" s="3">
+      <c r="B120" s="4">
         <v>46225.0</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D120" s="4">
+        <v>11</v>
+      </c>
+      <c r="D120" s="5">
         <v>1200.0</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2">
         <v>46225.37948128472</v>
       </c>
-      <c r="B121" s="3">
+      <c r="B121" s="4">
         <v>46225.0</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D121" s="4">
+        <v>20</v>
+      </c>
+      <c r="D121" s="5">
         <v>110.0</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2">
         <v>46225.37951672454</v>
       </c>
-      <c r="B122" s="3">
+      <c r="B122" s="4">
         <v>46225.0</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D122" s="4">
+      <c r="D122" s="5">
         <v>1100.0</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2">
         <v>46225.37954480324</v>
       </c>
-      <c r="B123" s="3">
+      <c r="B123" s="4">
         <v>46225.0</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D123" s="4">
+        <v>22</v>
+      </c>
+      <c r="D123" s="5">
         <v>110.0</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2">
         <v>46225.379571736106</v>
       </c>
-      <c r="B124" s="3">
+      <c r="B124" s="4">
         <v>46225.0</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D124" s="4">
+        <v>25</v>
+      </c>
+      <c r="D124" s="5">
         <v>110.0</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2">
         <v>46225.37959408565</v>
       </c>
-      <c r="B125" s="3">
+      <c r="B125" s="4">
         <v>46225.0</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D125" s="4">
+        <v>29</v>
+      </c>
+      <c r="D125" s="5">
         <v>110.0</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2">
         <v>46225.379621203705</v>
       </c>
-      <c r="B126" s="3">
+      <c r="B126" s="4">
         <v>46225.0</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D126" s="4">
+        <v>30</v>
+      </c>
+      <c r="D126" s="5">
         <v>110.0</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2">
         <v>46225.37967087963</v>
       </c>
-      <c r="B127" s="3">
+      <c r="B127" s="4">
         <v>46225.0</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D127" s="4">
+        <v>16</v>
+      </c>
+      <c r="D127" s="5">
         <v>500.0</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2">
         <v>46225.379873935184</v>
       </c>
-      <c r="B128" s="3">
+      <c r="B128" s="4">
         <v>46225.0</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D128" s="4">
+        <v>32</v>
+      </c>
+      <c r="D128" s="5">
         <v>95.0</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2">
         <v>46225.37993333333</v>
       </c>
-      <c r="B129" s="3">
+      <c r="B129" s="4">
         <v>46225.0</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D129" s="4">
+        <v>39</v>
+      </c>
+      <c r="D129" s="5">
         <v>1.0</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2">
         <v>46225.56209415509</v>
       </c>
-      <c r="B130" s="3">
+      <c r="B130" s="4">
         <v>46225.0</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D130" s="4">
+        <v>35</v>
+      </c>
+      <c r="D130" s="5">
         <v>3.0</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2">
         <v>46225.570436180555</v>
       </c>
-      <c r="B131" s="3">
+      <c r="B131" s="4">
         <v>46225.0</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D131" s="4">
+        <v>19</v>
+      </c>
+      <c r="D131" s="5">
         <v>200.0</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2">
         <v>46225.579509675925</v>
       </c>
-      <c r="B132" s="3">
+      <c r="B132" s="4">
         <v>46225.0</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D132" s="4">
+        <v>37</v>
+      </c>
+      <c r="D132" s="5">
         <v>50.0</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2">
         <v>46225.69770467593</v>
       </c>
-      <c r="B133" s="3">
+      <c r="B133" s="4">
         <v>46225.0</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D133" s="4">
+        <v>27</v>
+      </c>
+      <c r="D133" s="5">
         <v>110.0</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2">
         <v>46225.704650555555</v>
       </c>
-      <c r="B134" s="3">
+      <c r="B134" s="4">
         <v>46225.0</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D134" s="4">
+        <v>37</v>
+      </c>
+      <c r="D134" s="5">
         <v>50.0</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2">
         <v>46225.71850549769</v>
       </c>
-      <c r="B135" s="3">
+      <c r="B135" s="4">
         <v>46225.0</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D135" s="4">
+        <v>33</v>
+      </c>
+      <c r="D135" s="5">
         <v>21.0</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2">
         <v>46225.76829121528</v>
       </c>
-      <c r="B136" s="3">
+      <c r="B136" s="4">
         <v>46225.0</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D136" s="4">
+        <v>13</v>
+      </c>
+      <c r="D136" s="5">
         <v>189.0</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2">
         <v>46225.81627668982</v>
       </c>
-      <c r="B137" s="3">
+      <c r="B137" s="4">
         <v>46225.0</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D137" s="4">
+        <v>13</v>
+      </c>
+      <c r="D137" s="5">
         <v>110.0</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>156</v>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2">
+        <v>46226.32840304398</v>
+      </c>
+      <c r="B138" s="4">
+        <v>46226.0</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D138" s="5">
+        <v>400.0</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2">
+        <v>46226.32846012732</v>
+      </c>
+      <c r="B139" s="4">
+        <v>46226.0</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D139" s="5">
+        <v>500.0</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2">
+        <v>46226.373014756944</v>
+      </c>
+      <c r="B140" s="4">
+        <v>46226.0</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D140" s="5">
+        <v>110.0</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2">
+        <v>46226.37304784722</v>
+      </c>
+      <c r="B141" s="4">
+        <v>46226.0</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D141" s="5">
+        <v>1100.0</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2">
+        <v>46226.37309228009</v>
+      </c>
+      <c r="B142" s="4">
+        <v>46226.0</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D142" s="5">
+        <v>110.0</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2">
+        <v>46226.37311237269</v>
+      </c>
+      <c r="B143" s="4">
+        <v>46226.0</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D143" s="5">
+        <v>100.0</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2">
+        <v>46226.37314657407</v>
+      </c>
+      <c r="B144" s="4">
+        <v>46226.0</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D144" s="5">
+        <v>110.0</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2">
+        <v>46226.37319622685</v>
+      </c>
+      <c r="B145" s="4">
+        <v>46226.0</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D145" s="5">
+        <v>110.0</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2">
+        <v>46226.373261712964</v>
+      </c>
+      <c r="B146" s="4">
+        <v>46226.0</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D146" s="5">
+        <v>100.0</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2">
+        <v>46226.37330467593</v>
+      </c>
+      <c r="B147" s="4">
+        <v>46226.0</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D147" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2">
+        <v>46226.53193599537</v>
+      </c>
+      <c r="B148" s="4">
+        <v>46226.0</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D148" s="5">
+        <v>600.0</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2">
+        <v>46226.531970729164</v>
+      </c>
+      <c r="B149" s="4">
+        <v>46226.0</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D149" s="5">
+        <v>110.0</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2">
+        <v>46226.542640694446</v>
+      </c>
+      <c r="B150" s="4">
+        <v>46226.0</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D150" s="5">
+        <v>5.0</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2">
+        <v>46226.60987680555</v>
+      </c>
+      <c r="B151" s="4">
+        <v>46226.0</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D151" s="5">
+        <v>100.0</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2">
+        <v>46226.76189243056</v>
+      </c>
+      <c r="B152" s="4">
+        <v>46226.0</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D152" s="5">
+        <v>300.0</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2">
+        <v>46226.76422456019</v>
+      </c>
+      <c r="B153" s="4">
+        <v>46226.0</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D153" s="5">
+        <v>21.0</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -3164,186 +3484,186 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>157</v>
+        <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>158</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="5">
+        <v>11</v>
+      </c>
+      <c r="B2" s="3">
         <v>2382681.0</v>
       </c>
-      <c r="C2" s="4">
-        <v>12380.0</v>
+      <c r="C2" s="5">
+        <v>12880.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B3" s="6">
         <v>2778093.0</v>
       </c>
-      <c r="C3" s="4">
-        <v>4370.0</v>
+      <c r="C3" s="5">
+        <v>4970.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="5">
+        <v>19</v>
+      </c>
+      <c r="B4" s="3">
         <v>158521.0</v>
       </c>
-      <c r="C4" s="4">
-        <v>2200.0</v>
+      <c r="C4" s="5">
+        <v>2500.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="5">
+        <v>22</v>
+      </c>
+      <c r="B5" s="3">
         <v>169321.0</v>
       </c>
-      <c r="C5" s="4">
-        <v>1320.0</v>
+      <c r="C5" s="5">
+        <v>1430.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B6" s="6">
         <v>5820554.0</v>
       </c>
-      <c r="C6" s="4">
-        <v>880.0</v>
+      <c r="C6" s="5">
+        <v>980.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B7" s="6">
         <v>1425700.0</v>
       </c>
-      <c r="C7" s="4">
-        <v>1650.0</v>
+      <c r="C7" s="5">
+        <v>1760.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="5">
+        <v>29</v>
+      </c>
+      <c r="B8" s="3">
         <v>890948.0</v>
       </c>
-      <c r="C8" s="4">
-        <v>880.0</v>
+      <c r="C8" s="5">
+        <v>990.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="5">
+        <v>30</v>
+      </c>
+      <c r="B9" s="3">
         <v>552569.0</v>
       </c>
-      <c r="C9" s="4">
-        <v>880.0</v>
+      <c r="C9" s="5">
+        <v>990.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B10" s="6">
         <v>139781.0</v>
       </c>
-      <c r="C10" s="4">
-        <v>803.0</v>
+      <c r="C10" s="5">
+        <v>903.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="5">
+        <v>33</v>
+      </c>
+      <c r="B11" s="3">
         <v>9031.0</v>
       </c>
-      <c r="C11" s="4">
-        <v>168.0</v>
+      <c r="C11" s="5">
+        <v>189.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="3">
         <v>1123250.0</v>
       </c>
-      <c r="C12" s="4">
-        <v>8800.0</v>
+      <c r="C12" s="5">
+        <v>9900.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="5">
+        <v>35</v>
+      </c>
+      <c r="B13" s="3">
         <v>1832.0</v>
       </c>
-      <c r="C13" s="4">
-        <v>22.0</v>
+      <c r="C13" s="5">
+        <v>27.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="5">
+        <v>37</v>
+      </c>
+      <c r="B14" s="3">
         <v>8100.0</v>
       </c>
-      <c r="C14" s="4">
-        <v>750.0</v>
+      <c r="C14" s="5">
+        <v>850.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="5">
+        <v>39</v>
+      </c>
+      <c r="B15" s="3">
         <v>639.0</v>
       </c>
-      <c r="C15" s="4">
-        <v>8.0</v>
+      <c r="C15" s="5">
+        <v>9.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="5">
+        <v>20</v>
+      </c>
+      <c r="B16" s="3">
         <v>219463.0</v>
       </c>
-      <c r="C16" s="4">
-        <v>880.0</v>
+      <c r="C16" s="5">
+        <v>990.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B17" s="1">
         <v>0.0</v>
       </c>
-      <c r="C17" s="4">
-        <v>2529.0</v>
+      <c r="C17" s="5">
+        <v>2929.0</v>
       </c>
     </row>
   </sheetData>
@@ -3366,24 +3686,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>159</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>160</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>161</v>
+        <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>162</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>163</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B2" s="1">
         <v>330.0</v>
@@ -3395,14 +3715,14 @@
         <v>100.0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>164</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="4">
+        <v>11</v>
+      </c>
+      <c r="B3" s="5">
         <v>3000.0</v>
       </c>
       <c r="C3" s="1">
@@ -3412,12 +3732,12 @@
         <v>1000.0</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>165</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B4" s="1">
         <v>110.0</v>
@@ -3429,80 +3749,80 @@
         <v>1.0</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>165</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="5">
         <v>1100.0</v>
       </c>
-      <c r="C5" s="4">
-        <v>110.0</v>
-      </c>
-      <c r="D5" s="4">
+      <c r="C5" s="5">
+        <v>110.0</v>
+      </c>
+      <c r="D5" s="5">
         <v>100.0</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>166</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="4">
+        <v>22</v>
+      </c>
+      <c r="B6" s="5">
         <v>220.0</v>
       </c>
-      <c r="C6" s="4">
-        <v>110.0</v>
-      </c>
-      <c r="D6" s="4">
+      <c r="C6" s="5">
+        <v>110.0</v>
+      </c>
+      <c r="D6" s="5">
         <v>10.0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>165</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="4">
-        <v>110.0</v>
-      </c>
-      <c r="C7" s="4">
+        <v>25</v>
+      </c>
+      <c r="B7" s="5">
+        <v>110.0</v>
+      </c>
+      <c r="C7" s="5">
         <v>100.0</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="5">
         <v>10.0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>165</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="5">
+        <v>110.0</v>
+      </c>
+      <c r="C8" s="5">
+        <v>100.0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>10.0</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B8" s="4">
-        <v>110.0</v>
-      </c>
-      <c r="C8" s="4">
-        <v>100.0</v>
-      </c>
-      <c r="D8" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B9" s="1">
         <v>220.0</v>
@@ -3514,29 +3834,29 @@
         <v>100.0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>165</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="4">
+        <v>16</v>
+      </c>
+      <c r="B10" s="5">
         <v>550.0</v>
       </c>
       <c r="C10" s="1">
         <v>500.0</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="5">
         <v>100.0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>165</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B11" s="1">
         <v>550.0</v>
@@ -3544,113 +3864,113 @@
       <c r="C11" s="1">
         <v>110.0</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="5">
         <v>100.0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>165</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="4">
+        <v>19</v>
+      </c>
+      <c r="B12" s="5">
         <v>330.0</v>
       </c>
       <c r="C12" s="1">
         <v>300.0</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="5">
         <v>100.0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>165</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="4">
-        <v>110.0</v>
-      </c>
-      <c r="C13" s="4">
+        <v>32</v>
+      </c>
+      <c r="B13" s="5">
+        <v>110.0</v>
+      </c>
+      <c r="C13" s="5">
         <v>100.0</v>
       </c>
       <c r="D13" s="1">
         <v>90.0</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="4">
+        <v>33</v>
+      </c>
+      <c r="B14" s="5">
         <v>21.0</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="5">
         <v>7.0</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="5">
         <v>1.0</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B15" s="1">
         <v>5.0</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="5">
         <v>3.0</v>
       </c>
       <c r="D15" s="1">
         <v>1.0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>166</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="4">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5">
         <v>100.0</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="5">
         <v>50.0</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="5">
         <v>10.0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>167</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="4">
+        <v>39</v>
+      </c>
+      <c r="B17" s="5">
         <v>1.0</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="5">
         <v>3.0</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="5">
         <v>7.0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>167</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/backup/mantra-records.xlsx
+++ b/backup/mantra-records.xlsx
@@ -13,44 +13,44 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="200">
   <si>
     <t>时间戳</t>
   </si>
   <si>
+    <t>类别</t>
+  </si>
+  <si>
+    <t>历史基数</t>
+  </si>
+  <si>
+    <t>日期</t>
+  </si>
+  <si>
+    <t>应用累计</t>
+  </si>
+  <si>
+    <t>莲师心咒</t>
+  </si>
+  <si>
+    <t>数量</t>
+  </si>
+  <si>
+    <t>记录ID</t>
+  </si>
+  <si>
     <t>类别名称</t>
   </si>
   <si>
-    <t>类别</t>
-  </si>
-  <si>
-    <t>日期</t>
-  </si>
-  <si>
     <t>快捷按钮1</t>
   </si>
   <si>
-    <t>历史基数</t>
-  </si>
-  <si>
     <t>快捷按钮2</t>
   </si>
   <si>
-    <t>应用累计</t>
-  </si>
-  <si>
-    <t>数量</t>
-  </si>
-  <si>
     <t>快捷按钮3</t>
   </si>
   <si>
-    <t>记录ID</t>
-  </si>
-  <si>
-    <t>莲师心咒</t>
-  </si>
-  <si>
     <t>组别</t>
   </si>
   <si>
@@ -60,39 +60,45 @@
     <t>金刚桥</t>
   </si>
   <si>
+    <t>心咒</t>
+  </si>
+  <si>
+    <t>邬金空行</t>
+  </si>
+  <si>
+    <t>地藏圣号</t>
+  </si>
+  <si>
+    <t>圣号与礼赞</t>
+  </si>
+  <si>
+    <t>地藏心咒</t>
+  </si>
+  <si>
+    <t>观音心咒</t>
+  </si>
+  <si>
+    <t>绿度母心咒</t>
+  </si>
+  <si>
+    <t>文殊心咒</t>
+  </si>
+  <si>
     <t>mrlks9td-k4uqs3</t>
   </si>
   <si>
-    <t>绿度母心咒</t>
-  </si>
-  <si>
-    <t>心咒</t>
+    <t>黑财神心咒</t>
+  </si>
+  <si>
+    <t>普巴金刚心咒</t>
   </si>
   <si>
     <t>mrlksetf-hs5dn5</t>
   </si>
   <si>
-    <t>普巴金刚心咒</t>
-  </si>
-  <si>
-    <t>邬金空行</t>
-  </si>
-  <si>
     <t>mrlkt29s-qamx95</t>
   </si>
   <si>
-    <t>地藏心咒</t>
-  </si>
-  <si>
-    <t>地藏圣号</t>
-  </si>
-  <si>
-    <t>圣号与礼赞</t>
-  </si>
-  <si>
-    <t>观音心咒</t>
-  </si>
-  <si>
     <t>mrlkt5q5-bxqyk5</t>
   </si>
   <si>
@@ -102,12 +108,6 @@
     <t>mrlkt9ek-k7mk8m</t>
   </si>
   <si>
-    <t>文殊心咒</t>
-  </si>
-  <si>
-    <t>黑财神心咒</t>
-  </si>
-  <si>
     <t>mrlktc1w-fikhnq</t>
   </si>
   <si>
@@ -120,12 +120,12 @@
     <t>mrlktf0r-4v8u9r</t>
   </si>
   <si>
+    <t>mrlktosu-qse7qm</t>
+  </si>
+  <si>
     <t>21度母礼赞</t>
   </si>
   <si>
-    <t>mrlktosu-qse7qm</t>
-  </si>
-  <si>
     <t>无死长寿祈祷文</t>
   </si>
   <si>
@@ -565,6 +565,54 @@
   </si>
   <si>
     <t>mrx8rbuy-ex1nqu</t>
+  </si>
+  <si>
+    <t>mry43fbz-uoqz4c</t>
+  </si>
+  <si>
+    <t>mry43mjc-k338e4</t>
+  </si>
+  <si>
+    <t>mry43pc0-bp3y6n</t>
+  </si>
+  <si>
+    <t>mry43upv-o8zcot</t>
+  </si>
+  <si>
+    <t>mrylbq1z-67izvu</t>
+  </si>
+  <si>
+    <t>mrylf1tk-wa3wxq</t>
+  </si>
+  <si>
+    <t>mrylmx7l-zz7u9q</t>
+  </si>
+  <si>
+    <t>mrylomn3-ums4oq</t>
+  </si>
+  <si>
+    <t>mryncamq-9kwpiw</t>
+  </si>
+  <si>
+    <t>mryngnuq-2184kw</t>
+  </si>
+  <si>
+    <t>mrynjmqi-ln0nkc</t>
+  </si>
+  <si>
+    <t>mrynlu1i-4wb2tr</t>
+  </si>
+  <si>
+    <t>mryptqjv-71hr8w</t>
+  </si>
+  <si>
+    <t>mryptyvu-5qqu0o</t>
+  </si>
+  <si>
+    <t>mryzrpsc-7rgg7k</t>
+  </si>
+  <si>
+    <t>mryzrs05-eb10uw</t>
   </si>
 </sst>
 </file>
@@ -618,16 +666,16 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="14" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -870,111 +918,111 @@
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2">
+      <c r="A2" s="4">
         <v>46218.59993390046</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="5">
         <v>46218.0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="5">
+        <v>5</v>
+      </c>
+      <c r="D2" s="3">
         <v>2200.0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2">
+      <c r="A3" s="4">
         <v>46218.60000892361</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="5">
         <v>46218.0</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="5">
+        <v>21</v>
+      </c>
+      <c r="D3" s="3">
         <v>500.0</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2">
+      <c r="A4" s="4">
         <v>46218.60036074074</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="5">
         <v>46218.0</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="3">
+        <v>330.0</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4">
+        <v>46218.60041255787</v>
+      </c>
+      <c r="B5" s="5">
+        <v>46218.0</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="5">
-        <v>330.0</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2">
-        <v>46218.60041255787</v>
-      </c>
-      <c r="B5" s="4">
+      <c r="D5" s="3">
+        <v>220.0</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4">
+        <v>46218.60046773148</v>
+      </c>
+      <c r="B6" s="5">
         <v>46218.0</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="5">
-        <v>220.0</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2">
-        <v>46218.60046773148</v>
-      </c>
-      <c r="B6" s="4">
+      <c r="C6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="3">
+        <v>110.0</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4">
+        <v>46218.60050746528</v>
+      </c>
+      <c r="B7" s="5">
         <v>46218.0</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="5">
-        <v>110.0</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2">
-        <v>46218.60050746528</v>
-      </c>
-      <c r="B7" s="4">
-        <v>46218.0</v>
-      </c>
       <c r="C7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="5">
+        <v>29</v>
+      </c>
+      <c r="D7" s="3">
         <v>110.0</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -982,16 +1030,16 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2">
+      <c r="A8" s="4">
         <v>46218.600551979165</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="5">
         <v>46218.0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="5">
+        <v>22</v>
+      </c>
+      <c r="D8" s="3">
         <v>110.0</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -999,33 +1047,33 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2">
+      <c r="A9" s="4">
         <v>46218.60069868056</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="5">
         <v>46218.0</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="3">
         <v>90.0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2">
+      <c r="A10" s="4">
         <v>46218.60081484954</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="5">
         <v>46218.0</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="5">
+        <v>24</v>
+      </c>
+      <c r="D10" s="3">
         <v>110.0</v>
       </c>
       <c r="E10" s="1" t="s">
@@ -1033,16 +1081,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2">
+      <c r="A11" s="4">
         <v>46218.60088034722</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="5">
         <v>46218.0</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="5">
+        <v>17</v>
+      </c>
+      <c r="D11" s="3">
         <v>1100.0</v>
       </c>
       <c r="E11" s="1" t="s">
@@ -1050,16 +1098,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2">
+      <c r="A12" s="4">
         <v>46218.60112648148</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="5">
         <v>46218.0</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="3">
         <v>1.0</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -1067,16 +1115,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2">
+      <c r="A13" s="4">
         <v>46218.6012544213</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="5">
         <v>46218.0</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="5">
+        <v>16</v>
+      </c>
+      <c r="D13" s="3">
         <v>110.0</v>
       </c>
       <c r="E13" s="1" t="s">
@@ -1084,16 +1132,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2">
+      <c r="A14" s="4">
         <v>46218.60229002315</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="5">
         <v>46218.0</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="3">
         <v>50.0</v>
       </c>
       <c r="E14" s="1" t="s">
@@ -1101,16 +1149,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2">
+      <c r="A15" s="4">
         <v>46218.879222777774</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="5">
         <v>46218.0</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="3">
         <v>21.0</v>
       </c>
       <c r="E15" s="1" t="s">
@@ -1118,16 +1166,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2">
+      <c r="A16" s="4">
         <v>46218.87955795139</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="5">
         <v>46218.0</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16" s="5">
+        <v>36</v>
+      </c>
+      <c r="D16" s="3">
         <v>1.0</v>
       </c>
       <c r="E16" s="1" t="s">
@@ -1135,16 +1183,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2">
+      <c r="A17" s="4">
         <v>46219.36083100694</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="5">
         <v>46219.0</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="5">
+        <v>5</v>
+      </c>
+      <c r="D17" s="3">
         <v>2200.0</v>
       </c>
       <c r="E17" s="1" t="s">
@@ -1152,16 +1200,16 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2">
+      <c r="A18" s="4">
         <v>46219.36095940972</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="5">
         <v>46219.0</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="5">
+        <v>19</v>
+      </c>
+      <c r="D18" s="3">
         <v>220.0</v>
       </c>
       <c r="E18" s="1" t="s">
@@ -1169,16 +1217,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2">
+      <c r="A19" s="4">
         <v>46219.36098726852</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="5">
         <v>46219.0</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="5">
+        <v>20</v>
+      </c>
+      <c r="D19" s="3">
         <v>110.0</v>
       </c>
       <c r="E19" s="1" t="s">
@@ -1186,16 +1234,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2">
+      <c r="A20" s="4">
         <v>46219.36102891204</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="5">
         <v>46219.0</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20" s="5">
+        <v>22</v>
+      </c>
+      <c r="D20" s="3">
         <v>110.0</v>
       </c>
       <c r="E20" s="1" t="s">
@@ -1203,16 +1251,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2">
+      <c r="A21" s="4">
         <v>46219.361140196765</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="5">
         <v>46219.0</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" s="5">
+        <v>24</v>
+      </c>
+      <c r="D21" s="3">
         <v>110.0</v>
       </c>
       <c r="E21" s="1" t="s">
@@ -1220,16 +1268,16 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2">
+      <c r="A22" s="4">
         <v>46219.36120090278</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="5">
         <v>46219.0</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" s="5">
+        <v>17</v>
+      </c>
+      <c r="D22" s="3">
         <v>1100.0</v>
       </c>
       <c r="E22" s="1" t="s">
@@ -1237,16 +1285,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2">
+      <c r="A23" s="4">
         <v>46219.361246134256</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="5">
         <v>46219.0</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23" s="3">
         <v>1.0</v>
       </c>
       <c r="E23" s="1" t="s">
@@ -1254,16 +1302,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2">
+      <c r="A24" s="4">
         <v>46219.36128604166</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="5">
         <v>46219.0</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" s="5">
+        <v>16</v>
+      </c>
+      <c r="D24" s="3">
         <v>110.0</v>
       </c>
       <c r="E24" s="1" t="s">
@@ -1271,16 +1319,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2">
+      <c r="A25" s="4">
         <v>46219.36148746528</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="5">
         <v>46219.0</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25" s="3">
         <v>90.0</v>
       </c>
       <c r="E25" s="1" t="s">
@@ -1288,16 +1336,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2">
+      <c r="A26" s="4">
         <v>46219.37500490741</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="5">
         <v>46219.0</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D26" s="5">
+        <v>21</v>
+      </c>
+      <c r="D26" s="3">
         <v>500.0</v>
       </c>
       <c r="E26" s="1" t="s">
@@ -1305,16 +1353,16 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2">
+      <c r="A27" s="4">
         <v>46219.378031932865</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B27" s="5">
         <v>46219.0</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D27" s="5">
+        <v>29</v>
+      </c>
+      <c r="D27" s="3">
         <v>110.0</v>
       </c>
       <c r="E27" s="1" t="s">
@@ -1322,16 +1370,16 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2">
+      <c r="A28" s="4">
         <v>46219.53696891204</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28" s="5">
         <v>46219.0</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D28" s="5">
+        <v>36</v>
+      </c>
+      <c r="D28" s="3">
         <v>3.0</v>
       </c>
       <c r="E28" s="1" t="s">
@@ -1339,16 +1387,16 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2">
+      <c r="A29" s="4">
         <v>46219.57221748843</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29" s="5">
         <v>46219.0</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="5">
+        <v>25</v>
+      </c>
+      <c r="D29" s="3">
         <v>300.0</v>
       </c>
       <c r="E29" s="1" t="s">
@@ -1356,16 +1404,16 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2">
+      <c r="A30" s="4">
         <v>46219.572925706016</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B30" s="5">
         <v>46219.0</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D30" s="5">
+      <c r="D30" s="3">
         <v>21.0</v>
       </c>
       <c r="E30" s="1" t="s">
@@ -1373,16 +1421,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2">
+      <c r="A31" s="4">
         <v>46219.582504375</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B31" s="5">
         <v>46219.0</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D31" s="5">
+      <c r="D31" s="3">
         <v>100.0</v>
       </c>
       <c r="E31" s="1" t="s">
@@ -1390,16 +1438,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2">
+      <c r="A32" s="4">
         <v>46220.39272579861</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32" s="5">
         <v>46220.0</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D32" s="5">
+      <c r="D32" s="3">
         <v>330.0</v>
       </c>
       <c r="E32" s="1" t="s">
@@ -1407,16 +1455,16 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2">
+      <c r="A33" s="4">
         <v>46220.39278981481</v>
       </c>
-      <c r="B33" s="4">
+      <c r="B33" s="5">
         <v>46220.0</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D33" s="5">
+        <v>5</v>
+      </c>
+      <c r="D33" s="3">
         <v>330.0</v>
       </c>
       <c r="E33" s="1" t="s">
@@ -1424,16 +1472,16 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2">
+      <c r="A34" s="4">
         <v>46220.392932083334</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34" s="5">
         <v>46220.0</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D34" s="5">
+        <v>17</v>
+      </c>
+      <c r="D34" s="3">
         <v>1100.0</v>
       </c>
       <c r="E34" s="1" t="s">
@@ -1441,16 +1489,16 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2">
+      <c r="A35" s="4">
         <v>46220.392972974536</v>
       </c>
-      <c r="B35" s="4">
+      <c r="B35" s="5">
         <v>46220.0</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D35" s="5">
+        <v>19</v>
+      </c>
+      <c r="D35" s="3">
         <v>110.0</v>
       </c>
       <c r="E35" s="1" t="s">
@@ -1458,16 +1506,16 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2">
+      <c r="A36" s="4">
         <v>46220.39300672454</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B36" s="5">
         <v>46220.0</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D36" s="5">
+        <v>20</v>
+      </c>
+      <c r="D36" s="3">
         <v>110.0</v>
       </c>
       <c r="E36" s="1" t="s">
@@ -1475,16 +1523,16 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2">
+      <c r="A37" s="4">
         <v>46220.393032708336</v>
       </c>
-      <c r="B37" s="4">
+      <c r="B37" s="5">
         <v>46220.0</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D37" s="5">
+        <v>22</v>
+      </c>
+      <c r="D37" s="3">
         <v>110.0</v>
       </c>
       <c r="E37" s="1" t="s">
@@ -1492,16 +1540,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2">
+      <c r="A38" s="4">
         <v>46220.39306212963</v>
       </c>
-      <c r="B38" s="4">
+      <c r="B38" s="5">
         <v>46220.0</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D38" s="5">
+        <v>24</v>
+      </c>
+      <c r="D38" s="3">
         <v>110.0</v>
       </c>
       <c r="E38" s="1" t="s">
@@ -1509,16 +1557,16 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2">
+      <c r="A39" s="4">
         <v>46220.39315246527</v>
       </c>
-      <c r="B39" s="4">
+      <c r="B39" s="5">
         <v>46220.0</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D39" s="5">
+        <v>21</v>
+      </c>
+      <c r="D39" s="3">
         <v>500.0</v>
       </c>
       <c r="E39" s="1" t="s">
@@ -1526,16 +1574,16 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2">
+      <c r="A40" s="4">
         <v>46220.3932059375</v>
       </c>
-      <c r="B40" s="4">
+      <c r="B40" s="5">
         <v>46220.0</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D40" s="5">
+        <v>29</v>
+      </c>
+      <c r="D40" s="3">
         <v>110.0</v>
       </c>
       <c r="E40" s="1" t="s">
@@ -1543,16 +1591,16 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2">
+      <c r="A41" s="4">
         <v>46220.39326859954</v>
       </c>
-      <c r="B41" s="4">
+      <c r="B41" s="5">
         <v>46220.0</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D41" s="5">
+      <c r="D41" s="3">
         <v>90.0</v>
       </c>
       <c r="E41" s="1" t="s">
@@ -1560,16 +1608,16 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2">
+      <c r="A42" s="4">
         <v>46220.39332800926</v>
       </c>
-      <c r="B42" s="4">
+      <c r="B42" s="5">
         <v>46220.0</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D42" s="5">
+      <c r="D42" s="3">
         <v>1.0</v>
       </c>
       <c r="E42" s="1" t="s">
@@ -1577,16 +1625,16 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2">
+      <c r="A43" s="4">
         <v>46220.53172856482</v>
       </c>
-      <c r="B43" s="4">
+      <c r="B43" s="5">
         <v>46220.0</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D43" s="5">
+        <v>5</v>
+      </c>
+      <c r="D43" s="3">
         <v>500.0</v>
       </c>
       <c r="E43" s="1" t="s">
@@ -1594,16 +1642,16 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2">
+      <c r="A44" s="4">
         <v>46220.53914545139</v>
       </c>
-      <c r="B44" s="4">
+      <c r="B44" s="5">
         <v>46220.0</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D44" s="5">
+        <v>5</v>
+      </c>
+      <c r="D44" s="3">
         <v>350.0</v>
       </c>
       <c r="E44" s="1" t="s">
@@ -1611,16 +1659,16 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2">
+      <c r="A45" s="4">
         <v>46220.56417989584</v>
       </c>
-      <c r="B45" s="4">
+      <c r="B45" s="5">
         <v>46220.0</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D45" s="5">
+        <v>25</v>
+      </c>
+      <c r="D45" s="3">
         <v>300.0</v>
       </c>
       <c r="E45" s="1" t="s">
@@ -1628,16 +1676,16 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2">
+      <c r="A46" s="4">
         <v>46220.566308622685</v>
       </c>
-      <c r="B46" s="4">
+      <c r="B46" s="5">
         <v>46220.0</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D46" s="5">
+        <v>36</v>
+      </c>
+      <c r="D46" s="3">
         <v>3.0</v>
       </c>
       <c r="E46" s="1" t="s">
@@ -1645,16 +1693,16 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2">
+      <c r="A47" s="4">
         <v>46220.60263800926</v>
       </c>
-      <c r="B47" s="4">
+      <c r="B47" s="5">
         <v>46220.0</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D47" s="5">
+      <c r="D47" s="3">
         <v>100.0</v>
       </c>
       <c r="E47" s="1" t="s">
@@ -1662,16 +1710,16 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2">
+      <c r="A48" s="4">
         <v>46220.61828956018</v>
       </c>
-      <c r="B48" s="4">
+      <c r="B48" s="5">
         <v>46220.0</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D48" s="5">
+      <c r="D48" s="3">
         <v>21.0</v>
       </c>
       <c r="E48" s="1" t="s">
@@ -1679,16 +1727,16 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2">
+      <c r="A49" s="4">
         <v>46220.78008434028</v>
       </c>
-      <c r="B49" s="4">
+      <c r="B49" s="5">
         <v>46220.0</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D49" s="5">
+      <c r="D49" s="3">
         <v>100.0</v>
       </c>
       <c r="E49" s="1" t="s">
@@ -1696,16 +1744,16 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2">
+      <c r="A50" s="4">
         <v>46220.9643725</v>
       </c>
-      <c r="B50" s="4">
+      <c r="B50" s="5">
         <v>46220.0</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D50" s="5">
+        <v>16</v>
+      </c>
+      <c r="D50" s="3">
         <v>110.0</v>
       </c>
       <c r="E50" s="1" t="s">
@@ -1713,16 +1761,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2">
+      <c r="A51" s="4">
         <v>46221.481308622686</v>
       </c>
-      <c r="B51" s="4">
+      <c r="B51" s="5">
         <v>46221.0</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D51" s="5">
+      <c r="D51" s="3">
         <v>350.0</v>
       </c>
       <c r="E51" s="1" t="s">
@@ -1730,16 +1778,16 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2">
+      <c r="A52" s="4">
         <v>46221.481428680556</v>
       </c>
-      <c r="B52" s="4">
+      <c r="B52" s="5">
         <v>46221.0</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D52" s="5">
+      <c r="D52" s="3">
         <v>110.0</v>
       </c>
       <c r="E52" s="1" t="s">
@@ -1747,16 +1795,16 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2">
+      <c r="A53" s="4">
         <v>46221.52650024305</v>
       </c>
-      <c r="B53" s="4">
+      <c r="B53" s="5">
         <v>46221.0</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D53" s="5">
+        <v>5</v>
+      </c>
+      <c r="D53" s="3">
         <v>2200.0</v>
       </c>
       <c r="E53" s="1" t="s">
@@ -1764,16 +1812,16 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2">
+      <c r="A54" s="4">
         <v>46221.52749582176</v>
       </c>
-      <c r="B54" s="4">
+      <c r="B54" s="5">
         <v>46221.0</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D54" s="5">
+        <v>16</v>
+      </c>
+      <c r="D54" s="3">
         <v>110.0</v>
       </c>
       <c r="E54" s="1" t="s">
@@ -1781,16 +1829,16 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2">
+      <c r="A55" s="4">
         <v>46221.52754980324</v>
       </c>
-      <c r="B55" s="4">
+      <c r="B55" s="5">
         <v>46221.0</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D55" s="5">
+        <v>20</v>
+      </c>
+      <c r="D55" s="3">
         <v>110.0</v>
       </c>
       <c r="E55" s="1" t="s">
@@ -1798,16 +1846,16 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2">
+      <c r="A56" s="4">
         <v>46221.527581296294</v>
       </c>
-      <c r="B56" s="4">
+      <c r="B56" s="5">
         <v>46221.0</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D56" s="5">
+        <v>22</v>
+      </c>
+      <c r="D56" s="3">
         <v>110.0</v>
       </c>
       <c r="E56" s="1" t="s">
@@ -1815,16 +1863,16 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2">
+      <c r="A57" s="4">
         <v>46221.527755613424</v>
       </c>
-      <c r="B57" s="4">
+      <c r="B57" s="5">
         <v>46221.0</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D57" s="5">
+        <v>24</v>
+      </c>
+      <c r="D57" s="3">
         <v>110.0</v>
       </c>
       <c r="E57" s="1" t="s">
@@ -1832,16 +1880,16 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2">
+      <c r="A58" s="4">
         <v>46221.52786003472</v>
       </c>
-      <c r="B58" s="4">
+      <c r="B58" s="5">
         <v>46221.0</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D58" s="5">
+      <c r="D58" s="3">
         <v>1.0</v>
       </c>
       <c r="E58" s="1" t="s">
@@ -1849,16 +1897,16 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2">
+      <c r="A59" s="4">
         <v>46221.56208596065</v>
       </c>
-      <c r="B59" s="4">
+      <c r="B59" s="5">
         <v>46221.0</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D59" s="5">
+        <v>17</v>
+      </c>
+      <c r="D59" s="3">
         <v>1100.0</v>
       </c>
       <c r="E59" s="1" t="s">
@@ -1866,16 +1914,16 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2">
+      <c r="A60" s="4">
         <v>46221.562139201385</v>
       </c>
-      <c r="B60" s="4">
+      <c r="B60" s="5">
         <v>46221.0</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D60" s="5">
+        <v>19</v>
+      </c>
+      <c r="D60" s="3">
         <v>220.0</v>
       </c>
       <c r="E60" s="1" t="s">
@@ -1883,16 +1931,16 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2">
+      <c r="A61" s="4">
         <v>46221.56227361111</v>
       </c>
-      <c r="B61" s="4">
+      <c r="B61" s="5">
         <v>46221.0</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D61" s="5">
+        <v>21</v>
+      </c>
+      <c r="D61" s="3">
         <v>1100.0</v>
       </c>
       <c r="E61" s="1" t="s">
@@ -1900,16 +1948,16 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2">
+      <c r="A62" s="4">
         <v>46221.59101953704</v>
       </c>
-      <c r="B62" s="4">
+      <c r="B62" s="5">
         <v>46221.0</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D62" s="5">
+        <v>29</v>
+      </c>
+      <c r="D62" s="3">
         <v>880.0</v>
       </c>
       <c r="E62" s="1" t="s">
@@ -1917,16 +1965,16 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2">
+      <c r="A63" s="4">
         <v>46221.59110706019</v>
       </c>
-      <c r="B63" s="4">
+      <c r="B63" s="5">
         <v>46221.0</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D63" s="5">
+      <c r="D63" s="3">
         <v>100.0</v>
       </c>
       <c r="E63" s="1" t="s">
@@ -1934,16 +1982,16 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2">
+      <c r="A64" s="4">
         <v>46221.591245868054</v>
       </c>
-      <c r="B64" s="4">
+      <c r="B64" s="5">
         <v>46221.0</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D64" s="5">
+        <v>36</v>
+      </c>
+      <c r="D64" s="3">
         <v>5.0</v>
       </c>
       <c r="E64" s="1" t="s">
@@ -1951,16 +1999,16 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2">
+      <c r="A65" s="4">
         <v>46221.59138636574</v>
       </c>
-      <c r="B65" s="4">
+      <c r="B65" s="5">
         <v>46221.0</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D65" s="5">
+        <v>25</v>
+      </c>
+      <c r="D65" s="3">
         <v>330.0</v>
       </c>
       <c r="E65" s="1" t="s">
@@ -1968,16 +2016,16 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2">
+      <c r="A66" s="4">
         <v>46221.5952940625</v>
       </c>
-      <c r="B66" s="4">
+      <c r="B66" s="5">
         <v>46221.0</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D66" s="5">
+      <c r="D66" s="3">
         <v>21.0</v>
       </c>
       <c r="E66" s="1" t="s">
@@ -1985,16 +2033,16 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2">
+      <c r="A67" s="4">
         <v>46222.55562850695</v>
       </c>
-      <c r="B67" s="4">
+      <c r="B67" s="5">
         <v>46222.0</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D67" s="5">
+      <c r="D67" s="3">
         <v>300.0</v>
       </c>
       <c r="E67" s="1" t="s">
@@ -2002,16 +2050,16 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2">
+      <c r="A68" s="4">
         <v>46222.555725659724</v>
       </c>
-      <c r="B68" s="4">
+      <c r="B68" s="5">
         <v>46222.0</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D68" s="5">
+        <v>5</v>
+      </c>
+      <c r="D68" s="3">
         <v>1100.0</v>
       </c>
       <c r="E68" s="1" t="s">
@@ -2019,16 +2067,16 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2">
+      <c r="A69" s="4">
         <v>46222.555776423615</v>
       </c>
-      <c r="B69" s="4">
+      <c r="B69" s="5">
         <v>46222.0</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D69" s="5">
+        <v>20</v>
+      </c>
+      <c r="D69" s="3">
         <v>110.0</v>
       </c>
       <c r="E69" s="1" t="s">
@@ -2036,16 +2084,16 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2">
+      <c r="A70" s="4">
         <v>46222.55580371528</v>
       </c>
-      <c r="B70" s="4">
+      <c r="B70" s="5">
         <v>46222.0</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D70" s="5">
+        <v>22</v>
+      </c>
+      <c r="D70" s="3">
         <v>110.0</v>
       </c>
       <c r="E70" s="1" t="s">
@@ -2053,16 +2101,16 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2">
+      <c r="A71" s="4">
         <v>46222.55584842592</v>
       </c>
-      <c r="B71" s="4">
+      <c r="B71" s="5">
         <v>46222.0</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D71" s="5">
+        <v>24</v>
+      </c>
+      <c r="D71" s="3">
         <v>110.0</v>
       </c>
       <c r="E71" s="1" t="s">
@@ -2070,16 +2118,16 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2">
+      <c r="A72" s="4">
         <v>46222.55593107639</v>
       </c>
-      <c r="B72" s="4">
+      <c r="B72" s="5">
         <v>46222.0</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D72" s="5">
+      <c r="D72" s="3">
         <v>1.0</v>
       </c>
       <c r="E72" s="1" t="s">
@@ -2087,16 +2135,16 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2">
+      <c r="A73" s="4">
         <v>46222.566782037036</v>
       </c>
-      <c r="B73" s="4">
+      <c r="B73" s="5">
         <v>46222.0</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D73" s="5">
+        <v>16</v>
+      </c>
+      <c r="D73" s="3">
         <v>110.0</v>
       </c>
       <c r="E73" s="1" t="s">
@@ -2104,16 +2152,16 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2">
+      <c r="A74" s="4">
         <v>46222.566821898145</v>
       </c>
-      <c r="B74" s="4">
+      <c r="B74" s="5">
         <v>46222.0</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D74" s="5">
+        <v>17</v>
+      </c>
+      <c r="D74" s="3">
         <v>1100.0</v>
       </c>
       <c r="E74" s="1" t="s">
@@ -2121,16 +2169,16 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2">
+      <c r="A75" s="4">
         <v>46222.566868657406</v>
       </c>
-      <c r="B75" s="4">
+      <c r="B75" s="5">
         <v>46222.0</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D75" s="5">
+        <v>19</v>
+      </c>
+      <c r="D75" s="3">
         <v>110.0</v>
       </c>
       <c r="E75" s="1" t="s">
@@ -2138,16 +2186,16 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2">
+      <c r="A76" s="4">
         <v>46222.56694369213</v>
       </c>
-      <c r="B76" s="4">
+      <c r="B76" s="5">
         <v>46222.0</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D76" s="5">
+        <v>21</v>
+      </c>
+      <c r="D76" s="3">
         <v>110.0</v>
       </c>
       <c r="E76" s="1" t="s">
@@ -2155,16 +2203,16 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2">
+      <c r="A77" s="4">
         <v>46222.56698377315</v>
       </c>
-      <c r="B77" s="4">
+      <c r="B77" s="5">
         <v>46222.0</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D77" s="5">
+        <v>29</v>
+      </c>
+      <c r="D77" s="3">
         <v>110.0</v>
       </c>
       <c r="E77" s="1" t="s">
@@ -2172,16 +2220,16 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2">
+      <c r="A78" s="4">
         <v>46222.5670393287</v>
       </c>
-      <c r="B78" s="4">
+      <c r="B78" s="5">
         <v>46222.0</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D78" s="5">
+        <v>36</v>
+      </c>
+      <c r="D78" s="3">
         <v>1.0</v>
       </c>
       <c r="E78" s="1" t="s">
@@ -2189,16 +2237,16 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2">
+      <c r="A79" s="4">
         <v>46222.667202881945</v>
       </c>
-      <c r="B79" s="4">
+      <c r="B79" s="5">
         <v>46222.0</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D79" s="5">
+        <v>25</v>
+      </c>
+      <c r="D79" s="3">
         <v>110.0</v>
       </c>
       <c r="E79" s="1" t="s">
@@ -2206,16 +2254,16 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2">
+      <c r="A80" s="4">
         <v>46222.676215150466</v>
       </c>
-      <c r="B80" s="4">
+      <c r="B80" s="5">
         <v>46222.0</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D80" s="5">
+      <c r="D80" s="3">
         <v>21.0</v>
       </c>
       <c r="E80" s="1" t="s">
@@ -2223,16 +2271,16 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2">
+      <c r="A81" s="4">
         <v>46222.89222185186</v>
       </c>
-      <c r="B81" s="4">
+      <c r="B81" s="5">
         <v>46222.0</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D81" s="5">
+      <c r="D81" s="3">
         <v>220.0</v>
       </c>
       <c r="E81" s="1" t="s">
@@ -2240,16 +2288,16 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2">
+      <c r="A82" s="4">
         <v>46222.90832773148</v>
       </c>
-      <c r="B82" s="4">
+      <c r="B82" s="5">
         <v>46222.0</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D82" s="5">
+      <c r="D82" s="3">
         <v>108.0</v>
       </c>
       <c r="E82" s="1" t="s">
@@ -2257,16 +2305,16 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2">
+      <c r="A83" s="4">
         <v>46222.917884560185</v>
       </c>
-      <c r="B83" s="4">
+      <c r="B83" s="5">
         <v>46222.0</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D83" s="5">
+      <c r="D83" s="3">
         <v>100.0</v>
       </c>
       <c r="E83" s="1" t="s">
@@ -2274,16 +2322,16 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2">
+      <c r="A84" s="4">
         <v>46223.35147047453</v>
       </c>
-      <c r="B84" s="4">
+      <c r="B84" s="5">
         <v>46223.0</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D84" s="5">
+      <c r="D84" s="3">
         <v>330.0</v>
       </c>
       <c r="E84" s="1" t="s">
@@ -2291,16 +2339,16 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2">
+      <c r="A85" s="4">
         <v>46223.39655936343</v>
       </c>
-      <c r="B85" s="4">
+      <c r="B85" s="5">
         <v>46223.0</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D85" s="5">
+      <c r="D85" s="3">
         <v>110.0</v>
       </c>
       <c r="E85" s="1" t="s">
@@ -2308,16 +2356,16 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2">
+      <c r="A86" s="4">
         <v>46223.41721368056</v>
       </c>
-      <c r="B86" s="4">
+      <c r="B86" s="5">
         <v>46223.0</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D86" s="5">
+        <v>5</v>
+      </c>
+      <c r="D86" s="3">
         <v>1100.0</v>
       </c>
       <c r="E86" s="1" t="s">
@@ -2325,16 +2373,16 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2">
+      <c r="A87" s="4">
         <v>46223.41724953704</v>
       </c>
-      <c r="B87" s="4">
+      <c r="B87" s="5">
         <v>46223.0</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D87" s="5">
+        <v>16</v>
+      </c>
+      <c r="D87" s="3">
         <v>110.0</v>
       </c>
       <c r="E87" s="1" t="s">
@@ -2342,16 +2390,16 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2">
+      <c r="A88" s="4">
         <v>46223.41730127315</v>
       </c>
-      <c r="B88" s="4">
+      <c r="B88" s="5">
         <v>46223.0</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D88" s="5">
+        <v>20</v>
+      </c>
+      <c r="D88" s="3">
         <v>110.0</v>
       </c>
       <c r="E88" s="1" t="s">
@@ -2359,16 +2407,16 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2">
+      <c r="A89" s="4">
         <v>46223.41733108796</v>
       </c>
-      <c r="B89" s="4">
+      <c r="B89" s="5">
         <v>46223.0</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D89" s="5">
+        <v>22</v>
+      </c>
+      <c r="D89" s="3">
         <v>110.0</v>
       </c>
       <c r="E89" s="1" t="s">
@@ -2376,16 +2424,16 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2">
+      <c r="A90" s="4">
         <v>46223.417364733796</v>
       </c>
-      <c r="B90" s="4">
+      <c r="B90" s="5">
         <v>46223.0</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D90" s="5">
+        <v>24</v>
+      </c>
+      <c r="D90" s="3">
         <v>110.0</v>
       </c>
       <c r="E90" s="1" t="s">
@@ -2393,16 +2441,16 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2">
+      <c r="A91" s="4">
         <v>46223.417424976855</v>
       </c>
-      <c r="B91" s="4">
+      <c r="B91" s="5">
         <v>46223.0</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D91" s="5">
+      <c r="D91" s="3">
         <v>1.0</v>
       </c>
       <c r="E91" s="1" t="s">
@@ -2410,16 +2458,16 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2">
+      <c r="A92" s="4">
         <v>46223.427174247685</v>
       </c>
-      <c r="B92" s="4">
+      <c r="B92" s="5">
         <v>46223.0</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D92" s="5">
+        <v>17</v>
+      </c>
+      <c r="D92" s="3">
         <v>1100.0</v>
       </c>
       <c r="E92" s="1" t="s">
@@ -2427,16 +2475,16 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2">
+      <c r="A93" s="4">
         <v>46223.43069275463</v>
       </c>
-      <c r="B93" s="4">
+      <c r="B93" s="5">
         <v>46223.0</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D93" s="5">
+        <v>19</v>
+      </c>
+      <c r="D93" s="3">
         <v>110.0</v>
       </c>
       <c r="E93" s="1" t="s">
@@ -2444,16 +2492,16 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2">
+      <c r="A94" s="4">
         <v>46223.623396574076</v>
       </c>
-      <c r="B94" s="4">
+      <c r="B94" s="5">
         <v>46223.0</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D94" s="5">
+        <v>25</v>
+      </c>
+      <c r="D94" s="3">
         <v>330.0</v>
       </c>
       <c r="E94" s="1" t="s">
@@ -2461,16 +2509,16 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2">
+      <c r="A95" s="4">
         <v>46223.6235443287</v>
       </c>
-      <c r="B95" s="4">
+      <c r="B95" s="5">
         <v>46223.0</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D95" s="5">
+      <c r="D95" s="3">
         <v>50.0</v>
       </c>
       <c r="E95" s="1" t="s">
@@ -2478,16 +2526,16 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2">
+      <c r="A96" s="4">
         <v>46223.883227592596</v>
       </c>
-      <c r="B96" s="4">
+      <c r="B96" s="5">
         <v>46223.0</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D96" s="5">
+        <v>21</v>
+      </c>
+      <c r="D96" s="3">
         <v>660.0</v>
       </c>
       <c r="E96" s="1" t="s">
@@ -2495,16 +2543,16 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2">
+      <c r="A97" s="4">
         <v>46223.883269224534</v>
       </c>
-      <c r="B97" s="4">
+      <c r="B97" s="5">
         <v>46223.0</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D97" s="5">
+        <v>29</v>
+      </c>
+      <c r="D97" s="3">
         <v>110.0</v>
       </c>
       <c r="E97" s="1" t="s">
@@ -2512,16 +2560,16 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2">
+      <c r="A98" s="4">
         <v>46223.88392460648</v>
       </c>
-      <c r="B98" s="4">
+      <c r="B98" s="5">
         <v>46223.0</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D98" s="5">
+      <c r="D98" s="3">
         <v>21.0</v>
       </c>
       <c r="E98" s="1" t="s">
@@ -2529,16 +2577,16 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2">
+      <c r="A99" s="4">
         <v>46223.884048865744</v>
       </c>
-      <c r="B99" s="4">
+      <c r="B99" s="5">
         <v>46223.0</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D99" s="5">
+        <v>36</v>
+      </c>
+      <c r="D99" s="3">
         <v>1.0</v>
       </c>
       <c r="E99" s="1" t="s">
@@ -2546,16 +2594,16 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2">
+      <c r="A100" s="4">
         <v>46223.92497723379</v>
       </c>
-      <c r="B100" s="4">
+      <c r="B100" s="5">
         <v>46223.0</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D100" s="5">
+      <c r="D100" s="3">
         <v>50.0</v>
       </c>
       <c r="E100" s="1" t="s">
@@ -2563,16 +2611,16 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2">
+      <c r="A101" s="4">
         <v>46224.34672042824</v>
       </c>
-      <c r="B101" s="4">
+      <c r="B101" s="5">
         <v>46224.0</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D101" s="5">
+      <c r="D101" s="3">
         <v>160.0</v>
       </c>
       <c r="E101" s="1" t="s">
@@ -2580,16 +2628,16 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2">
+      <c r="A102" s="4">
         <v>46224.346837997684</v>
       </c>
-      <c r="B102" s="4">
+      <c r="B102" s="5">
         <v>46224.0</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D102" s="5">
+        <v>5</v>
+      </c>
+      <c r="D102" s="3">
         <v>1200.0</v>
       </c>
       <c r="E102" s="1" t="s">
@@ -2597,16 +2645,16 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2">
+      <c r="A103" s="4">
         <v>46224.348533703705</v>
       </c>
-      <c r="B103" s="4">
+      <c r="B103" s="5">
         <v>46224.0</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D103" s="5">
+        <v>16</v>
+      </c>
+      <c r="D103" s="3">
         <v>110.0</v>
       </c>
       <c r="E103" s="1" t="s">
@@ -2614,16 +2662,16 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2">
+      <c r="A104" s="4">
         <v>46224.34856788194</v>
       </c>
-      <c r="B104" s="4">
+      <c r="B104" s="5">
         <v>46224.0</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D104" s="5">
+        <v>17</v>
+      </c>
+      <c r="D104" s="3">
         <v>1100.0</v>
       </c>
       <c r="E104" s="1" t="s">
@@ -2631,16 +2679,16 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2">
+      <c r="A105" s="4">
         <v>46224.348606203705</v>
       </c>
-      <c r="B105" s="4">
+      <c r="B105" s="5">
         <v>46224.0</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D105" s="5">
+        <v>19</v>
+      </c>
+      <c r="D105" s="3">
         <v>220.0</v>
       </c>
       <c r="E105" s="1" t="s">
@@ -2648,16 +2696,16 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2">
+      <c r="A106" s="4">
         <v>46224.34863465278</v>
       </c>
-      <c r="B106" s="4">
+      <c r="B106" s="5">
         <v>46224.0</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D106" s="5">
+        <v>20</v>
+      </c>
+      <c r="D106" s="3">
         <v>110.0</v>
       </c>
       <c r="E106" s="1" t="s">
@@ -2665,16 +2713,16 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2">
+      <c r="A107" s="4">
         <v>46224.34865721065</v>
       </c>
-      <c r="B107" s="4">
+      <c r="B107" s="5">
         <v>46224.0</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D107" s="5">
+        <v>22</v>
+      </c>
+      <c r="D107" s="3">
         <v>110.0</v>
       </c>
       <c r="E107" s="1" t="s">
@@ -2682,16 +2730,16 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2">
+      <c r="A108" s="4">
         <v>46224.34868755787</v>
       </c>
-      <c r="B108" s="4">
+      <c r="B108" s="5">
         <v>46224.0</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D108" s="5">
+        <v>24</v>
+      </c>
+      <c r="D108" s="3">
         <v>110.0</v>
       </c>
       <c r="E108" s="1" t="s">
@@ -2699,16 +2747,16 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2">
+      <c r="A109" s="4">
         <v>46224.348736608794</v>
       </c>
-      <c r="B109" s="4">
+      <c r="B109" s="5">
         <v>46224.0</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D109" s="5">
+      <c r="D109" s="3">
         <v>1.0</v>
       </c>
       <c r="E109" s="1" t="s">
@@ -2716,16 +2764,16 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2">
+      <c r="A110" s="4">
         <v>46224.389971909724</v>
       </c>
-      <c r="B110" s="4">
+      <c r="B110" s="5">
         <v>46224.0</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D110" s="5">
+        <v>21</v>
+      </c>
+      <c r="D110" s="3">
         <v>500.0</v>
       </c>
       <c r="E110" s="1" t="s">
@@ -2733,16 +2781,16 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2">
+      <c r="A111" s="4">
         <v>46224.3899990162</v>
       </c>
-      <c r="B111" s="4">
+      <c r="B111" s="5">
         <v>46224.0</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D111" s="5">
+        <v>29</v>
+      </c>
+      <c r="D111" s="3">
         <v>110.0</v>
       </c>
       <c r="E111" s="1" t="s">
@@ -2750,16 +2798,16 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2">
+      <c r="A112" s="4">
         <v>46224.39007417824</v>
       </c>
-      <c r="B112" s="4">
+      <c r="B112" s="5">
         <v>46224.0</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D112" s="5">
+      <c r="D112" s="3">
         <v>110.0</v>
       </c>
       <c r="E112" s="1" t="s">
@@ -2767,16 +2815,16 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2">
+      <c r="A113" s="4">
         <v>46224.55259348379</v>
       </c>
-      <c r="B113" s="4">
+      <c r="B113" s="5">
         <v>46224.0</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D113" s="5">
+        <v>25</v>
+      </c>
+      <c r="D113" s="3">
         <v>300.0</v>
       </c>
       <c r="E113" s="1" t="s">
@@ -2784,16 +2832,16 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2">
+      <c r="A114" s="4">
         <v>46224.55264100694</v>
       </c>
-      <c r="B114" s="4">
+      <c r="B114" s="5">
         <v>46224.0</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D114" s="5">
+      <c r="D114" s="3">
         <v>100.0</v>
       </c>
       <c r="E114" s="1" t="s">
@@ -2801,16 +2849,16 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2">
+      <c r="A115" s="4">
         <v>46224.55486512731</v>
       </c>
-      <c r="B115" s="4">
+      <c r="B115" s="5">
         <v>46224.0</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D115" s="5">
+      <c r="D115" s="3">
         <v>21.0</v>
       </c>
       <c r="E115" s="1" t="s">
@@ -2818,16 +2866,16 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2">
+      <c r="A116" s="4">
         <v>46224.77226398148</v>
       </c>
-      <c r="B116" s="4">
+      <c r="B116" s="5">
         <v>46224.0</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D116" s="5">
+      <c r="D116" s="3">
         <v>150.0</v>
       </c>
       <c r="E116" s="1" t="s">
@@ -2835,16 +2883,16 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2">
+      <c r="A117" s="4">
         <v>46224.772311493056</v>
       </c>
-      <c r="B117" s="4">
+      <c r="B117" s="5">
         <v>46224.0</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D117" s="5">
+        <v>36</v>
+      </c>
+      <c r="D117" s="3">
         <v>5.0</v>
       </c>
       <c r="E117" s="1" t="s">
@@ -2852,16 +2900,16 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2">
+      <c r="A118" s="4">
         <v>46224.865057523144</v>
       </c>
-      <c r="B118" s="4">
+      <c r="B118" s="5">
         <v>46224.0</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D118" s="5">
+      <c r="D118" s="3">
         <v>110.0</v>
       </c>
       <c r="E118" s="1" t="s">
@@ -2869,16 +2917,16 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2">
+      <c r="A119" s="4">
         <v>46225.37715869213</v>
       </c>
-      <c r="B119" s="4">
+      <c r="B119" s="5">
         <v>46225.0</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D119" s="5">
+      <c r="D119" s="3">
         <v>180.0</v>
       </c>
       <c r="E119" s="1" t="s">
@@ -2886,16 +2934,16 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2">
+      <c r="A120" s="4">
         <v>46225.377258506946</v>
       </c>
-      <c r="B120" s="4">
+      <c r="B120" s="5">
         <v>46225.0</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D120" s="5">
+        <v>5</v>
+      </c>
+      <c r="D120" s="3">
         <v>1200.0</v>
       </c>
       <c r="E120" s="1" t="s">
@@ -2903,16 +2951,16 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2">
+      <c r="A121" s="4">
         <v>46225.37948128472</v>
       </c>
-      <c r="B121" s="4">
+      <c r="B121" s="5">
         <v>46225.0</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D121" s="5">
+        <v>16</v>
+      </c>
+      <c r="D121" s="3">
         <v>110.0</v>
       </c>
       <c r="E121" s="1" t="s">
@@ -2920,16 +2968,16 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2">
+      <c r="A122" s="4">
         <v>46225.37951672454</v>
       </c>
-      <c r="B122" s="4">
+      <c r="B122" s="5">
         <v>46225.0</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D122" s="5">
+        <v>17</v>
+      </c>
+      <c r="D122" s="3">
         <v>1100.0</v>
       </c>
       <c r="E122" s="1" t="s">
@@ -2937,16 +2985,16 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2">
+      <c r="A123" s="4">
         <v>46225.37954480324</v>
       </c>
-      <c r="B123" s="4">
+      <c r="B123" s="5">
         <v>46225.0</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D123" s="5">
+        <v>19</v>
+      </c>
+      <c r="D123" s="3">
         <v>110.0</v>
       </c>
       <c r="E123" s="1" t="s">
@@ -2954,16 +3002,16 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2">
+      <c r="A124" s="4">
         <v>46225.379571736106</v>
       </c>
-      <c r="B124" s="4">
+      <c r="B124" s="5">
         <v>46225.0</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D124" s="5">
+        <v>20</v>
+      </c>
+      <c r="D124" s="3">
         <v>110.0</v>
       </c>
       <c r="E124" s="1" t="s">
@@ -2971,16 +3019,16 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2">
+      <c r="A125" s="4">
         <v>46225.37959408565</v>
       </c>
-      <c r="B125" s="4">
+      <c r="B125" s="5">
         <v>46225.0</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D125" s="5">
+        <v>22</v>
+      </c>
+      <c r="D125" s="3">
         <v>110.0</v>
       </c>
       <c r="E125" s="1" t="s">
@@ -2988,16 +3036,16 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2">
+      <c r="A126" s="4">
         <v>46225.379621203705</v>
       </c>
-      <c r="B126" s="4">
+      <c r="B126" s="5">
         <v>46225.0</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D126" s="5">
+        <v>24</v>
+      </c>
+      <c r="D126" s="3">
         <v>110.0</v>
       </c>
       <c r="E126" s="1" t="s">
@@ -3005,16 +3053,16 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2">
+      <c r="A127" s="4">
         <v>46225.37967087963</v>
       </c>
-      <c r="B127" s="4">
+      <c r="B127" s="5">
         <v>46225.0</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D127" s="5">
+        <v>21</v>
+      </c>
+      <c r="D127" s="3">
         <v>500.0</v>
       </c>
       <c r="E127" s="1" t="s">
@@ -3022,16 +3070,16 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2">
+      <c r="A128" s="4">
         <v>46225.379873935184</v>
       </c>
-      <c r="B128" s="4">
+      <c r="B128" s="5">
         <v>46225.0</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D128" s="5">
+      <c r="D128" s="3">
         <v>95.0</v>
       </c>
       <c r="E128" s="1" t="s">
@@ -3039,16 +3087,16 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2">
+      <c r="A129" s="4">
         <v>46225.37993333333</v>
       </c>
-      <c r="B129" s="4">
+      <c r="B129" s="5">
         <v>46225.0</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D129" s="5">
+      <c r="D129" s="3">
         <v>1.0</v>
       </c>
       <c r="E129" s="1" t="s">
@@ -3056,16 +3104,16 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2">
+      <c r="A130" s="4">
         <v>46225.56209415509</v>
       </c>
-      <c r="B130" s="4">
+      <c r="B130" s="5">
         <v>46225.0</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D130" s="5">
+        <v>36</v>
+      </c>
+      <c r="D130" s="3">
         <v>3.0</v>
       </c>
       <c r="E130" s="1" t="s">
@@ -3073,16 +3121,16 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2">
+      <c r="A131" s="4">
         <v>46225.570436180555</v>
       </c>
-      <c r="B131" s="4">
+      <c r="B131" s="5">
         <v>46225.0</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D131" s="5">
+        <v>25</v>
+      </c>
+      <c r="D131" s="3">
         <v>200.0</v>
       </c>
       <c r="E131" s="1" t="s">
@@ -3090,16 +3138,16 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2">
+      <c r="A132" s="4">
         <v>46225.579509675925</v>
       </c>
-      <c r="B132" s="4">
+      <c r="B132" s="5">
         <v>46225.0</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D132" s="5">
+      <c r="D132" s="3">
         <v>50.0</v>
       </c>
       <c r="E132" s="1" t="s">
@@ -3107,16 +3155,16 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2">
+      <c r="A133" s="4">
         <v>46225.69770467593</v>
       </c>
-      <c r="B133" s="4">
+      <c r="B133" s="5">
         <v>46225.0</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D133" s="5">
+        <v>29</v>
+      </c>
+      <c r="D133" s="3">
         <v>110.0</v>
       </c>
       <c r="E133" s="1" t="s">
@@ -3124,16 +3172,16 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2">
+      <c r="A134" s="4">
         <v>46225.704650555555</v>
       </c>
-      <c r="B134" s="4">
+      <c r="B134" s="5">
         <v>46225.0</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D134" s="5">
+      <c r="D134" s="3">
         <v>50.0</v>
       </c>
       <c r="E134" s="1" t="s">
@@ -3141,16 +3189,16 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2">
+      <c r="A135" s="4">
         <v>46225.71850549769</v>
       </c>
-      <c r="B135" s="4">
+      <c r="B135" s="5">
         <v>46225.0</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D135" s="5">
+      <c r="D135" s="3">
         <v>21.0</v>
       </c>
       <c r="E135" s="1" t="s">
@@ -3158,16 +3206,16 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2">
+      <c r="A136" s="4">
         <v>46225.76829121528</v>
       </c>
-      <c r="B136" s="4">
+      <c r="B136" s="5">
         <v>46225.0</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D136" s="5">
+      <c r="D136" s="3">
         <v>189.0</v>
       </c>
       <c r="E136" s="1" t="s">
@@ -3175,16 +3223,16 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2">
+      <c r="A137" s="4">
         <v>46225.81627668982</v>
       </c>
-      <c r="B137" s="4">
+      <c r="B137" s="5">
         <v>46225.0</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D137" s="5">
+      <c r="D137" s="3">
         <v>110.0</v>
       </c>
       <c r="E137" s="1" t="s">
@@ -3192,16 +3240,16 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2">
+      <c r="A138" s="4">
         <v>46226.32840304398</v>
       </c>
-      <c r="B138" s="4">
+      <c r="B138" s="5">
         <v>46226.0</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D138" s="5">
+      <c r="D138" s="3">
         <v>400.0</v>
       </c>
       <c r="E138" s="1" t="s">
@@ -3209,16 +3257,16 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2">
+      <c r="A139" s="4">
         <v>46226.32846012732</v>
       </c>
-      <c r="B139" s="4">
+      <c r="B139" s="5">
         <v>46226.0</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D139" s="5">
+        <v>5</v>
+      </c>
+      <c r="D139" s="3">
         <v>500.0</v>
       </c>
       <c r="E139" s="1" t="s">
@@ -3226,16 +3274,16 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2">
+      <c r="A140" s="4">
         <v>46226.373014756944</v>
       </c>
-      <c r="B140" s="4">
+      <c r="B140" s="5">
         <v>46226.0</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D140" s="5">
+        <v>16</v>
+      </c>
+      <c r="D140" s="3">
         <v>110.0</v>
       </c>
       <c r="E140" s="1" t="s">
@@ -3243,16 +3291,16 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2">
+      <c r="A141" s="4">
         <v>46226.37304784722</v>
       </c>
-      <c r="B141" s="4">
+      <c r="B141" s="5">
         <v>46226.0</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D141" s="5">
+        <v>17</v>
+      </c>
+      <c r="D141" s="3">
         <v>1100.0</v>
       </c>
       <c r="E141" s="1" t="s">
@@ -3260,16 +3308,16 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2">
+      <c r="A142" s="4">
         <v>46226.37309228009</v>
       </c>
-      <c r="B142" s="4">
+      <c r="B142" s="5">
         <v>46226.0</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D142" s="5">
+        <v>19</v>
+      </c>
+      <c r="D142" s="3">
         <v>110.0</v>
       </c>
       <c r="E142" s="1" t="s">
@@ -3277,16 +3325,16 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2">
+      <c r="A143" s="4">
         <v>46226.37311237269</v>
       </c>
-      <c r="B143" s="4">
+      <c r="B143" s="5">
         <v>46226.0</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D143" s="5">
+        <v>20</v>
+      </c>
+      <c r="D143" s="3">
         <v>100.0</v>
       </c>
       <c r="E143" s="1" t="s">
@@ -3294,16 +3342,16 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2">
+      <c r="A144" s="4">
         <v>46226.37314657407</v>
       </c>
-      <c r="B144" s="4">
+      <c r="B144" s="5">
         <v>46226.0</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D144" s="5">
+        <v>22</v>
+      </c>
+      <c r="D144" s="3">
         <v>110.0</v>
       </c>
       <c r="E144" s="1" t="s">
@@ -3311,16 +3359,16 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2">
+      <c r="A145" s="4">
         <v>46226.37319622685</v>
       </c>
-      <c r="B145" s="4">
+      <c r="B145" s="5">
         <v>46226.0</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D145" s="5">
+        <v>24</v>
+      </c>
+      <c r="D145" s="3">
         <v>110.0</v>
       </c>
       <c r="E145" s="1" t="s">
@@ -3328,16 +3376,16 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2">
+      <c r="A146" s="4">
         <v>46226.373261712964</v>
       </c>
-      <c r="B146" s="4">
+      <c r="B146" s="5">
         <v>46226.0</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D146" s="5">
+      <c r="D146" s="3">
         <v>100.0</v>
       </c>
       <c r="E146" s="1" t="s">
@@ -3345,16 +3393,16 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2">
+      <c r="A147" s="4">
         <v>46226.37330467593</v>
       </c>
-      <c r="B147" s="4">
+      <c r="B147" s="5">
         <v>46226.0</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D147" s="5">
+      <c r="D147" s="3">
         <v>1.0</v>
       </c>
       <c r="E147" s="1" t="s">
@@ -3362,16 +3410,16 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2">
+      <c r="A148" s="4">
         <v>46226.53193599537</v>
       </c>
-      <c r="B148" s="4">
+      <c r="B148" s="5">
         <v>46226.0</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D148" s="5">
+        <v>21</v>
+      </c>
+      <c r="D148" s="3">
         <v>600.0</v>
       </c>
       <c r="E148" s="1" t="s">
@@ -3379,16 +3427,16 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2">
+      <c r="A149" s="4">
         <v>46226.531970729164</v>
       </c>
-      <c r="B149" s="4">
+      <c r="B149" s="5">
         <v>46226.0</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D149" s="5">
+        <v>29</v>
+      </c>
+      <c r="D149" s="3">
         <v>110.0</v>
       </c>
       <c r="E149" s="1" t="s">
@@ -3396,16 +3444,16 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2">
+      <c r="A150" s="4">
         <v>46226.542640694446</v>
       </c>
-      <c r="B150" s="4">
+      <c r="B150" s="5">
         <v>46226.0</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D150" s="5">
+        <v>36</v>
+      </c>
+      <c r="D150" s="3">
         <v>5.0</v>
       </c>
       <c r="E150" s="1" t="s">
@@ -3413,16 +3461,16 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2">
+      <c r="A151" s="4">
         <v>46226.60987680555</v>
       </c>
-      <c r="B151" s="4">
+      <c r="B151" s="5">
         <v>46226.0</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D151" s="5">
+      <c r="D151" s="3">
         <v>100.0</v>
       </c>
       <c r="E151" s="1" t="s">
@@ -3430,16 +3478,16 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2">
+      <c r="A152" s="4">
         <v>46226.76189243056</v>
       </c>
-      <c r="B152" s="4">
+      <c r="B152" s="5">
         <v>46226.0</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D152" s="5">
+        <v>25</v>
+      </c>
+      <c r="D152" s="3">
         <v>300.0</v>
       </c>
       <c r="E152" s="1" t="s">
@@ -3447,20 +3495,292 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2">
+      <c r="A153" s="4">
         <v>46226.76422456019</v>
       </c>
-      <c r="B153" s="4">
+      <c r="B153" s="5">
         <v>46226.0</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D153" s="5">
+      <c r="D153" s="3">
         <v>21.0</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>183</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="4">
+        <v>46227.37339665509</v>
+      </c>
+      <c r="B154" s="5">
+        <v>46227.0</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D154" s="3">
+        <v>370.0</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="4">
+        <v>46227.37350472222</v>
+      </c>
+      <c r="B155" s="5">
+        <v>46227.0</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D155" s="3">
+        <v>700.0</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="4">
+        <v>46227.37354666667</v>
+      </c>
+      <c r="B156" s="5">
+        <v>46227.0</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D156" s="3">
+        <v>1100.0</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="4">
+        <v>46227.373627442124</v>
+      </c>
+      <c r="B157" s="5">
+        <v>46227.0</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D157" s="3">
+        <v>60.0</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="4">
+        <v>46227.70835748843</v>
+      </c>
+      <c r="B158" s="5">
+        <v>46227.0</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D158" s="3">
+        <v>110.0</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="4">
+        <v>46227.71015398148</v>
+      </c>
+      <c r="B159" s="5">
+        <v>46227.0</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D159" s="3">
+        <v>110.0</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="4">
+        <v>46227.71440482639</v>
+      </c>
+      <c r="B160" s="5">
+        <v>46227.0</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D160" s="3">
+        <v>110.0</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4">
+        <v>46227.71532628472</v>
+      </c>
+      <c r="B161" s="5">
+        <v>46227.0</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D161" s="3">
+        <v>110.0</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="4">
+        <v>46227.747546134255</v>
+      </c>
+      <c r="B162" s="5">
+        <v>46227.0</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D162" s="3">
+        <v>110.0</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="4">
+        <v>46227.74990446759</v>
+      </c>
+      <c r="B163" s="5">
+        <v>46227.0</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D163" s="3">
+        <v>150.0</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="4">
+        <v>46227.75150770834</v>
+      </c>
+      <c r="B164" s="5">
+        <v>46227.0</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D164" s="3">
+        <v>110.0</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="4">
+        <v>46227.75269729167</v>
+      </c>
+      <c r="B165" s="5">
+        <v>46227.0</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D165" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="4">
+        <v>46227.79584494213</v>
+      </c>
+      <c r="B166" s="5">
+        <v>46227.0</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D166" s="3">
+        <v>300.0</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="4">
+        <v>46227.79596993055</v>
+      </c>
+      <c r="B167" s="5">
+        <v>46227.0</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D167" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="4">
+        <v>46227.98915347223</v>
+      </c>
+      <c r="B168" s="5">
+        <v>46227.0</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D168" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="4">
+        <v>46227.98918672454</v>
+      </c>
+      <c r="B169" s="5">
+        <v>46227.0</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D169" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -3481,101 +3801,101 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="3">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2">
         <v>2382681.0</v>
       </c>
-      <c r="C2" s="5">
-        <v>12880.0</v>
+      <c r="C2" s="3">
+        <v>13580.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B3" s="6">
         <v>2778093.0</v>
       </c>
-      <c r="C3" s="5">
-        <v>4970.0</v>
+      <c r="C3" s="3">
+        <v>5120.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="3">
+        <v>25</v>
+      </c>
+      <c r="B4" s="2">
         <v>158521.0</v>
       </c>
-      <c r="C4" s="5">
-        <v>2500.0</v>
+      <c r="C4" s="3">
+        <v>2800.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="3">
+        <v>19</v>
+      </c>
+      <c r="B5" s="2">
         <v>169321.0</v>
       </c>
-      <c r="C5" s="5">
-        <v>1430.0</v>
+      <c r="C5" s="3">
+        <v>1540.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B6" s="6">
         <v>5820554.0</v>
       </c>
-      <c r="C6" s="5">
-        <v>980.0</v>
+      <c r="C6" s="3">
+        <v>1090.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B7" s="6">
         <v>1425700.0</v>
       </c>
-      <c r="C7" s="5">
-        <v>1760.0</v>
+      <c r="C7" s="3">
+        <v>1870.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="3">
+        <v>22</v>
+      </c>
+      <c r="B8" s="2">
         <v>890948.0</v>
       </c>
-      <c r="C8" s="5">
-        <v>990.0</v>
+      <c r="C8" s="3">
+        <v>1100.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="3">
+        <v>24</v>
+      </c>
+      <c r="B9" s="2">
         <v>552569.0</v>
       </c>
-      <c r="C9" s="5">
-        <v>990.0</v>
+      <c r="C9" s="3">
+        <v>1100.0</v>
       </c>
     </row>
     <row r="10">
@@ -3585,74 +3905,74 @@
       <c r="B10" s="6">
         <v>139781.0</v>
       </c>
-      <c r="C10" s="5">
-        <v>903.0</v>
+      <c r="C10" s="3">
+        <v>963.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="2">
         <v>9031.0</v>
       </c>
-      <c r="C11" s="5">
-        <v>189.0</v>
+      <c r="C11" s="3">
+        <v>210.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="3">
+        <v>17</v>
+      </c>
+      <c r="B12" s="2">
         <v>1123250.0</v>
       </c>
-      <c r="C12" s="5">
-        <v>9900.0</v>
+      <c r="C12" s="3">
+        <v>11000.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="3">
+        <v>36</v>
+      </c>
+      <c r="B13" s="2">
         <v>1832.0</v>
       </c>
-      <c r="C13" s="5">
-        <v>27.0</v>
+      <c r="C13" s="3">
+        <v>32.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="2">
         <v>8100.0</v>
       </c>
-      <c r="C14" s="5">
-        <v>850.0</v>
+      <c r="C14" s="3">
+        <v>950.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="2">
         <v>639.0</v>
       </c>
-      <c r="C15" s="5">
-        <v>9.0</v>
+      <c r="C15" s="3">
+        <v>10.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="3">
+        <v>16</v>
+      </c>
+      <c r="B16" s="2">
         <v>219463.0</v>
       </c>
-      <c r="C16" s="5">
-        <v>990.0</v>
+      <c r="C16" s="3">
+        <v>1100.0</v>
       </c>
     </row>
     <row r="17">
@@ -3662,8 +3982,8 @@
       <c r="B17" s="1">
         <v>0.0</v>
       </c>
-      <c r="C17" s="5">
-        <v>2929.0</v>
+      <c r="C17" s="3">
+        <v>3299.0</v>
       </c>
     </row>
   </sheetData>
@@ -3686,16 +4006,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>12</v>
@@ -3720,9 +4040,9 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="5">
+        <v>5</v>
+      </c>
+      <c r="B3" s="3">
         <v>3000.0</v>
       </c>
       <c r="C3" s="1">
@@ -3732,12 +4052,12 @@
         <v>1000.0</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1">
         <v>110.0</v>
@@ -3749,80 +4069,80 @@
         <v>1.0</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="5">
+        <v>17</v>
+      </c>
+      <c r="B5" s="3">
         <v>1100.0</v>
       </c>
-      <c r="C5" s="5">
-        <v>110.0</v>
-      </c>
-      <c r="D5" s="5">
+      <c r="C5" s="3">
+        <v>110.0</v>
+      </c>
+      <c r="D5" s="3">
         <v>100.0</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="5">
+        <v>19</v>
+      </c>
+      <c r="B6" s="3">
         <v>220.0</v>
       </c>
-      <c r="C6" s="5">
-        <v>110.0</v>
-      </c>
-      <c r="D6" s="5">
+      <c r="C6" s="3">
+        <v>110.0</v>
+      </c>
+      <c r="D6" s="3">
         <v>10.0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="5">
-        <v>110.0</v>
-      </c>
-      <c r="C7" s="5">
+        <v>20</v>
+      </c>
+      <c r="B7" s="3">
+        <v>110.0</v>
+      </c>
+      <c r="C7" s="3">
         <v>100.0</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="3">
         <v>10.0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="5">
-        <v>110.0</v>
-      </c>
-      <c r="C8" s="5">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>110.0</v>
+      </c>
+      <c r="C8" s="3">
         <v>100.0</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="3">
         <v>10.0</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1">
         <v>220.0</v>
@@ -3834,29 +4154,29 @@
         <v>100.0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="5">
+        <v>21</v>
+      </c>
+      <c r="B10" s="3">
         <v>550.0</v>
       </c>
       <c r="C10" s="1">
         <v>500.0</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="3">
         <v>100.0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B11" s="1">
         <v>550.0</v>
@@ -3864,38 +4184,38 @@
       <c r="C11" s="1">
         <v>110.0</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="3">
         <v>100.0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="5">
+        <v>25</v>
+      </c>
+      <c r="B12" s="3">
         <v>330.0</v>
       </c>
       <c r="C12" s="1">
         <v>300.0</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="3">
         <v>100.0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="5">
-        <v>110.0</v>
-      </c>
-      <c r="C13" s="5">
+      <c r="B13" s="3">
+        <v>110.0</v>
+      </c>
+      <c r="C13" s="3">
         <v>100.0</v>
       </c>
       <c r="D13" s="1">
@@ -3909,13 +4229,13 @@
       <c r="A14" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="3">
         <v>21.0</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="3">
         <v>7.0</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="3">
         <v>1.0</v>
       </c>
       <c r="E14" s="1" t="s">
@@ -3924,32 +4244,32 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B15" s="1">
         <v>5.0</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="3">
         <v>3.0</v>
       </c>
       <c r="D15" s="1">
         <v>1.0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="3">
         <v>100.0</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="3">
         <v>50.0</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="3">
         <v>10.0</v>
       </c>
       <c r="E16" s="1" t="s">
@@ -3960,13 +4280,13 @@
       <c r="A17" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="3">
         <v>1.0</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="3">
         <v>3.0</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="3">
         <v>7.0</v>
       </c>
       <c r="E17" s="1" t="s">
